--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -13,6 +13,9 @@
     <sheet name="names" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="tags" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="tiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="attributes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="skills" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="figure" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1114,286 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>At or below this elevation the ground is wet. Water and moss appear here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roll.attribute_weight</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>How much a natural attribute is worth in a roll. A 10 in the attribute is worth 30 with this at 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>roll.skill_weight</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How much practice is worth in a roll. At 1, a skill of 100 is worth 100 -- practice eventually outweighs talent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>roll.noise_spread</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>22</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>How much luck swings a single attempt, either way. Lower makes the better character win more reliably.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>skill.cap</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The most practice any one skill can hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>learn.gain_on_failure</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a character learns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>learn.gain_on_success</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Practice gained from a successful attempt. Deliberately small -- succeeding teaches you very little.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>learn.near_miss_bonus</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>learn.near_miss_margin</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>How close a failure has to be to count as only just missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>actor.count</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>How many crawlers start in the chunk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>actor.attribute_min</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lowest a natural attribute can be rolled at. Ordinary people sit near 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>actor.attribute_max</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Highest a natural attribute can be rolled at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>actor.hat_chance</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>How many crawlers turn up already wearing something on their head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>actor.step_ticks</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>actor.height_m</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>How tall a grown crawler is. One tile is one metre, so this is how tall they look.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1196,8 +1479,28 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>figure.nominal_height_m</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>READ ONLY. The height the figure tab's part measurements are written against. A crawler of a different height has every part scaled by the same ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>READ ONLY -- these describe the shape of the world, not its balance. Changing one stops the build on purpose.</t>
         </is>
@@ -1214,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1338,6 +1641,66 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>nothing there</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ui.label_attributes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ui.label_skills</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ui.label_wearing</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>wearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ui.label_bare</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>character.name_pool</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bran, Ysolde, Corwin, Maerl, Thessa, Odric, Vela, Garn, Ketta, Rhodry, Isme, Dunmar, Sable, Wren, Halgar, Nix, Orla, Tam, Brennis, Sorrel</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1578,6 +1941,40 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Cannot be seen through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A thinking creature with the six attributes and skills of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>crawler</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>crawler</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>One of yours: came into the labyrinth, may yet leave it.</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1601,7 +1998,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1637,6 +2035,11 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1672,7 +2075,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Worked flagstone. The default footing of the labyrinth.</t>
         </is>
@@ -1709,7 +2115,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Trodden soil.</t>
         </is>
@@ -1746,7 +2155,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Stone gone green where the water sits.</t>
         </is>
@@ -1783,7 +2195,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Ankle deep. Slows a walker, ruins what it soaks.</t>
         </is>
@@ -1820,7 +2235,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Collapsed masonry, not yet cleared.</t>
         </is>
@@ -1857,7 +2275,10 @@
           <t>walk</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Somebody else got this far.</t>
         </is>
@@ -1894,7 +2315,10 @@
           <t>ramp</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>A climbable one-metre slope.</t>
         </is>
@@ -1931,9 +2355,460 @@
           <t>block</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>999</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>A full cubic metre of rock.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>abbrev</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>might</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MGT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Raw physical force. Lifting, hauling, forcing, and the heavy end of any tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>agility</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Speed and fine control. Keeping your feet, quick hands, delicate work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>endurance</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Endurance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Staying power. Long marches, cold nights, illness, a whole day of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>presence</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Presence</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Effect on other people. Singing, teaching, calming a panic, bargaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>intellect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Intellect</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What can be learned and worked out. Recipes, repairs, maps, lore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>willpower</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Willpower</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WIL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What can be made to happen anyway. Fear, pain, boredom, sticking at a hated task.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>derives</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clambering</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Clambering</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>agility:2,endurance:1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Keeping your feet on bad ground: water, rubble, moss, a steep ramp. Rolled every time a crawler tries to step onto a difficult tile.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>half_width</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>from_m</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>to_m</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>#33302c</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Always drawn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Torso</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>#5c5145</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Always drawn. The cloth colour, and the widest part of a crawler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>#ab977d</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Always drawn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hat</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>#23201d</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Only drawn on a crawler wearing one. Keep half_width near the head's or the brim hides the face. Rule 4: if it is on them, it is on screen -- add a row here and it can be worn.</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -16,6 +16,7 @@
     <sheet name="attributes" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="skills" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="figure" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="structures" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -720,13 +721,249 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>half_width</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>height_m</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Campfire</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>structure,fire,warm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>#b4541f</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>55</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The heart of a camp. Everything else is laid out around it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bedroll</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bedroll</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>structure,rest,cloth</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>#6b5a44</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Somewhere to sleep. The easiest thing in a camp to put up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>structure,store,wood</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>#5d4a30</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Keeps supplies off the wet floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>windbreak</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Windbreak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>structure,shelter,wood</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>#4f4436</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>65</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>The hardest thing in a starting camp, and the one that makes it feel like one.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -760,11 +997,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>render.low_width</t>
+          <t>render.tile_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>480</v>
+        <v>64</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -773,18 +1010,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Internal render width. The picture is drawn this small, then scaled up with hard pixel edges to get the sprite look.</t>
+          <t>Screen width of one square metre of ground. Twice tile_h makes the classic two-to-one isometric view.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>render.low_height</t>
+          <t>render.tile_h</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>270</v>
+        <v>32</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,14 +1030,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Internal render height. Keep the same shape as low_width (16:9) or the view letterboxes.</t>
+          <t>Screen height of one square metre of ground, seen from this angle.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>render.tile_w</t>
+          <t>render.rise</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -808,163 +1045,163 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>px/m</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Screen width of one 1m tile diamond at zoom 1.</t>
+          <t>LOCKED SCALE: how many pixels tall one metre is. Everything in the game is drawn against this, so a 1.6 m crawler is 52 px tall. Changing it rescales the entire world.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>render.tile_h</t>
+          <t>render.occluder_fade</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>0.28</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Screen height of one 1m tile diamond at zoom 1. Half of tile_w gives the classic 2:1 isometric view.</t>
+          <t>How solid a block stays when it is standing between you and the tile you are inspecting. 1 = never fades, 0 = disappears entirely.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>render.rise</t>
+          <t>render.side_shade_left</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>0.78</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>px/m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>How many pixels of screen height one metre of elevation is worth. Raise it to make the world feel taller and more vertical.</t>
+          <t>Brightness of the left-facing wall of a block. Below 1 makes it darker than the top.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>render.occluder_fade</t>
+          <t>render.side_shade_right</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>How solid a block stays when it is standing between you and the tile you are inspecting. 1 = never fades, 0 = disappears entirely.</t>
+          <t>Brightness of the right-facing wall of a block.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>render.side_shade_left</t>
+          <t>render.height_tint</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.78</v>
+        <v>0.035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x/m</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Brightness of the left-facing wall of a block. Below 1 makes it darker than the top.</t>
+          <t>How much lighter a surface gets per metre of elevation. Gives depth without lighting.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>render.side_shade_right</t>
+          <t>camera.key_pan_speed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5600000000000001</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>px/tick</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Brightness of the right-facing wall of a block.</t>
+          <t>How fast the arrow keys slide the view.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>render.height_tint</t>
+          <t>world.chunk_tiles</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.035</v>
+        <v>56</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>x/m</t>
+          <t>tiles</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>How much lighter a surface gets per metre of elevation. Gives depth without lighting.</t>
+          <t>Width and depth of the piece of labyrinth generated. 56 tiles = 56 metres across.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>camera.zoom_start</t>
+          <t>world.max_elevation</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zoom the game opens at.</t>
+          <t>How many different floor levels the rooms and halls are spread across.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>camera.zoom_min</t>
+          <t>roll.attribute_weight</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -973,18 +1210,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Furthest out you can zoom.</t>
+          <t>How much a natural attribute is worth in a roll. A 10 in the attribute is worth 30 with this at 3.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>camera.zoom_max</t>
+          <t>roll.skill_weight</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -993,178 +1230,178 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Closest in you can zoom. Whole numbers only, so pixels stay square. Zooming in shows fewer metres, not more detail.</t>
+          <t>How much practice is worth in a roll. At 1, a skill of 100 is worth 100 -- practice eventually outweighs talent.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>camera.key_pan_speed</t>
+          <t>roll.noise_spread</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>px/tick</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>How fast the arrow keys slide the view.</t>
+          <t>How much luck swings a single attempt, either way. Lower makes the better character win more reliably.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>world.chunk_tiles</t>
+          <t>skill.cap</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tiles</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Width and depth of the piece of labyrinth generated. 28 tiles = 28 metres across.</t>
+          <t>The most practice any one skill can hold.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>world.max_elevation</t>
+          <t>learn.gain_on_failure</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tallest the ground is allowed to get above the floor of a chunk.</t>
+          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a character learns.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>world.terrain_scale</t>
+          <t>learn.gain_on_success</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tiles</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Size of the lumps in the ground. Bigger = broader, smoother hills; smaller = choppier.</t>
+          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>world.ramp_chance</t>
+          <t>learn.near_miss_bonus</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>How often a one-metre step gets a ramp instead of being a wall you cannot climb.</t>
+          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>world.damp_level</t>
+          <t>learn.near_miss_margin</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>At or below this elevation the ground is wet. Water and moss appear here.</t>
+          <t>How close a failure has to be to count as only just missing.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>roll.attribute_weight</t>
+          <t>actor.count</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>people</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>How much a natural attribute is worth in a roll. A 10 in the attribute is worth 30 with this at 3.</t>
+          <t>How many crawlers turn up in the labyrinth.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>roll.skill_weight</t>
+          <t>actor.attribute_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>How much practice is worth in a roll. At 1, a skill of 100 is worth 100 -- practice eventually outweighs talent.</t>
+          <t>Lowest a natural attribute can be rolled at. Ordinary people sit near 10.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>roll.noise_spread</t>
+          <t>actor.attribute_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1173,114 +1410,114 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>How much luck swings a single attempt, either way. Lower makes the better character win more reliably.</t>
+          <t>Highest a natural attribute can be rolled at.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>skill.cap</t>
+          <t>actor.hat_chance</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The most practice any one skill can hold.</t>
+          <t>How many crawlers turn up already wearing something on their head.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>learn.gain_on_failure</t>
+          <t>actor.step_ticks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2</v>
+        <v>26</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a character learns.</t>
+          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>learn.gain_on_success</t>
+          <t>actor.height_m</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.35</v>
+        <v>1.625</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Practice gained from a successful attempt. Deliberately small -- succeeding teaches you very little.</t>
+          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>learn.near_miss_bonus</t>
+          <t>render.zoom_start</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
+          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>learn.near_miss_margin</t>
+          <t>render.zoom_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>How close a failure has to be to count as only just missing.</t>
+          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>actor.count</t>
+          <t>render.zoom_max</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1288,103 +1525,103 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>How many crawlers start in the chunk.</t>
+          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>actor.attribute_min</t>
+          <t>render.max_buffer_w</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>960</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lowest a natural attribute can be rolled at. Ordinary people sit near 10.</t>
+          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>actor.attribute_max</t>
+          <t>render.max_buffer_h</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16</v>
+        <v>540</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Highest a natural attribute can be rolled at.</t>
+          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>actor.hat_chance</t>
+          <t>time.coast_ticks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>How many crawlers turn up already wearing something on their head.</t>
+          <t>How long the world keeps running after you stop moving the view. 0 means time stops the instant you do.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>actor.step_ticks</t>
+          <t>world.rooms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
+          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>actor.height_m</t>
+          <t>world.room_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1393,7 +1630,227 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How tall a grown crawler is. One tile is one metre, so this is how tall they look.</t>
+          <t>Smallest a room can be, along one side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>world.room_max</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Largest a room can be, along one side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>world.hall_width</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>How wide the halls between rooms are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>world.rock_height</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>camp.bedrolls</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>beds</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>How many bedrolls the crawlers lay out around the fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>camp.stores</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>How many stores the crawlers put up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>camp.windbreaks</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>windbreaks</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>How many windbreaks the crawlers put up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>camp.site_spread</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>How far from the fire the rest of the camp is laid out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>camp.progress_per_success</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>25</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>camp.work_ticks</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>18</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>render.cutaway_fade</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>render.cutaway_depth</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1701,6 +2158,150 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>Bran, Ysolde, Corwin, Maerl, Thessa, Odric, Vela, Garn, Ketta, Rhodry, Isme, Dunmar, Sable, Wren, Halgar, Nix, Orla, Tam, Brennis, Sorrel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ui.label_progress</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ui.label_state</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ui.label_doing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>doing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ui.label_ground</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ui.state_planned</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>marked out, not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ui.state_clearing</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ground still needs clearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ui.state_building</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>going up</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ui.state_built</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ui.doing_walking</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>walking to the camp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ui.doing_clearing</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>clearing ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ui.doing_building</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ui.doing_idle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>looking about</t>
         </is>
       </c>
     </row>
@@ -1715,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1975,6 +2576,159 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>One of yours: came into the labyrinth, may yet leave it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Something raised by hand that was not there before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gives light and warmth, and will go out if nobody feeds it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Somewhere to sleep or recover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Keeps the weather and the dark off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Holds things so they are not carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Made of timber: burns, rots, can be repaired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cloth</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cloth</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Made of fabric: light, tears, soaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>unbuilt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>unbuilt</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Planned and marked out, but not finished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Holds off the cold. Crawlers will come to it.</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1999,7 +2753,8 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="78" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2040,6 +2795,11 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -2078,7 +2838,10 @@
       <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Worked flagstone. The default footing of the labyrinth.</t>
         </is>
@@ -2118,7 +2881,10 @@
       <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Trodden soil.</t>
         </is>
@@ -2158,7 +2924,10 @@
       <c r="G4" t="n">
         <v>16</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Stone gone green where the water sits.</t>
         </is>
@@ -2198,7 +2967,10 @@
       <c r="G5" t="n">
         <v>26</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>60</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Ankle deep. Slows a walker, ruins what it soaks.</t>
         </is>
@@ -2238,7 +3010,10 @@
       <c r="G6" t="n">
         <v>30</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Collapsed masonry, not yet cleared.</t>
         </is>
@@ -2278,7 +3053,10 @@
       <c r="G7" t="n">
         <v>14</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Somebody else got this far.</t>
         </is>
@@ -2318,7 +3096,10 @@
       <c r="G8" t="n">
         <v>22</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>A climbable one-metre slope.</t>
         </is>
@@ -2358,7 +3139,10 @@
       <c r="G9" t="n">
         <v>999</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>999</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>A full cubic metre of rock.</t>
         </is>
@@ -2549,7 +3333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2593,12 +3377,320 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>agility:2,endurance:1</t>
+          <t>might:1,agility:1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Keeping your feet on bad ground: water, rubble, moss, a steep ramp. Rolled every time a crawler tries to step onto a difficult tile.</t>
+          <t>Climbing, scrambling, and keeping your feet on ground that does not want you to. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>labouring</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Labouring</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>might:1,endurance:1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hauling, digging, clearing ground, and still doing it an hour later. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wrangling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wrangling</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>might:1,presence:1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Handling animals, and dragging people out of trouble whether they like it or not. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>might:1,intellect:1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Raising structures that stay up. Knowing where the weight goes, and being able to put it there. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fighting</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fighting</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>might:1,willpower:1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The one fifth of the game that is violence. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ranging</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ranging</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>agility:1,endurance:1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Covering ground: travelling far, moving quietly, getting back again. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>performing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Performing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>agility:1,presence:1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Singing, playing, dancing, and holding a room while you do it. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>crafting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Crafting</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>agility:1,intellect:1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Making and mending: tools, clothes, meals, anything that takes hands and a recipe. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tinkering</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tinkering</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>agility:1,willpower:1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Locks, traps, and anything fiddly that punishes a shaking hand. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tending</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tending</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>endurance:1,presence:1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nursing, feeding, and keeping people upright who would rather lie down. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>foraging</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Foraging</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>endurance:1,intellect:1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hunting, fishing, gathering, and knowing which of it is safe to eat. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>enduring</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Enduring</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>endurance:1,willpower:1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cold, hunger, pain, boredom and the dark. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bargaining</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bargaining</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>presence:1,intellect:1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Trading, persuading, and working out what somebody actually wants. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>leading</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Leading</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>presence:1,willpower:1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rallying, calming a panic, and holding a group together when it wants to scatter. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>studying</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Studying</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>intellect:1,willpower:1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lore, mapmaking, deciphering, and sitting with a problem until it gives. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -963,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1017,7 +1017,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>render.tile_h</t>
+          <t>render.rise</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1025,63 +1025,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>px/m</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Screen height of one square metre of ground, seen from this angle.</t>
+          <t>LOCKED SCALE: how many pixels tall one metre is. Everything in the game is drawn against this, so a 1.6 m crawler is 52 px tall. Changing it rescales the entire world.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>render.rise</t>
+          <t>render.occluder_fade</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>0.28</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>px/m</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LOCKED SCALE: how many pixels tall one metre is. Everything in the game is drawn against this, so a 1.6 m crawler is 52 px tall. Changing it rescales the entire world.</t>
+          <t>How solid a block stays when it is standing between you and the tile you are inspecting. 1 = never fades, 0 = disappears entirely.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>render.occluder_fade</t>
+          <t>render.side_shade_left</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.28</v>
+        <v>0.78</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>How solid a block stays when it is standing between you and the tile you are inspecting. 1 = never fades, 0 = disappears entirely.</t>
+          <t>Brightness of the left-facing wall of a block. Below 1 makes it darker than the top.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>render.side_shade_left</t>
+          <t>render.side_shade_right</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1090,118 +1090,118 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brightness of the left-facing wall of a block. Below 1 makes it darker than the top.</t>
+          <t>Brightness of the right-facing wall of a block.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>render.side_shade_right</t>
+          <t>render.height_tint</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x/m</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brightness of the right-facing wall of a block.</t>
+          <t>How much lighter a surface gets per metre of elevation. Gives depth without lighting.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>render.height_tint</t>
+          <t>camera.key_pan_speed</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.035</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x/m</t>
+          <t>px/tick</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>How much lighter a surface gets per metre of elevation. Gives depth without lighting.</t>
+          <t>How fast the arrow keys slide the view.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>camera.key_pan_speed</t>
+          <t>world.chunk_tiles</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>px/tick</t>
+          <t>tiles</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>How fast the arrow keys slide the view.</t>
+          <t>Width and depth of the piece of labyrinth generated. 56 tiles = 56 metres across.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>world.chunk_tiles</t>
+          <t>world.max_elevation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tiles</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Width and depth of the piece of labyrinth generated. 56 tiles = 56 metres across.</t>
+          <t>How many different floor levels the rooms and halls are spread across.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>world.max_elevation</t>
+          <t>roll.attribute_weight</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>How many different floor levels the rooms and halls are spread across.</t>
+          <t>How much a natural attribute is worth in a roll. A 10 in the attribute is worth 30 with this at 3.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>roll.attribute_weight</t>
+          <t>roll.skill_weight</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1210,38 +1210,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>How much a natural attribute is worth in a roll. A 10 in the attribute is worth 30 with this at 3.</t>
+          <t>How much practice is worth in a roll. At 1, a skill of 100 is worth 100 -- practice eventually outweighs talent.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>roll.skill_weight</t>
+          <t>roll.noise_spread</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>How much practice is worth in a roll. At 1, a skill of 100 is worth 100 -- practice eventually outweighs talent.</t>
+          <t>How much luck swings a single attempt, either way. Lower makes the better character win more reliably.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>roll.noise_spread</t>
+          <t>skill.cap</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1250,18 +1250,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>How much luck swings a single attempt, either way. Lower makes the better character win more reliably.</t>
+          <t>The most practice any one skill can hold.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>skill.cap</t>
+          <t>learn.gain_on_failure</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>2.2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1270,18 +1270,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The most practice any one skill can hold.</t>
+          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a character learns.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>learn.gain_on_failure</t>
+          <t>learn.gain_on_success</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a character learns.</t>
+          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>learn.gain_on_success</t>
+          <t>learn.near_miss_bonus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1310,18 +1310,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
+          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>learn.near_miss_bonus</t>
+          <t>learn.near_miss_margin</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1330,58 +1330,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
+          <t>How close a failure has to be to count as only just missing.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>learn.near_miss_margin</t>
+          <t>actor.count</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>people</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>How close a failure has to be to count as only just missing.</t>
+          <t>How many crawlers turn up in the labyrinth.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>actor.count</t>
+          <t>actor.attribute_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>How many crawlers turn up in the labyrinth.</t>
+          <t>Lowest a natural attribute can be rolled at. Ordinary people sit near 10.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>actor.attribute_min</t>
+          <t>actor.attribute_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1390,98 +1390,98 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lowest a natural attribute can be rolled at. Ordinary people sit near 10.</t>
+          <t>Highest a natural attribute can be rolled at.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>actor.attribute_max</t>
+          <t>actor.hat_chance</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>0.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Highest a natural attribute can be rolled at.</t>
+          <t>How many crawlers turn up already wearing something on their head.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>actor.hat_chance</t>
+          <t>actor.step_ticks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5</v>
+        <v>26</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>How many crawlers turn up already wearing something on their head.</t>
+          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>actor.step_ticks</t>
+          <t>actor.height_m</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>1.625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
+          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>actor.height_m</t>
+          <t>render.zoom_start</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
+          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>render.zoom_start</t>
+          <t>render.zoom_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1490,18 +1490,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
+          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>render.zoom_min</t>
+          <t>render.zoom_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1510,38 +1510,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
+          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>render.zoom_max</t>
+          <t>render.max_buffer_w</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>960</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
+          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>render.max_buffer_w</t>
+          <t>render.max_buffer_h</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>960</v>
+        <v>540</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1550,78 +1550,78 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
+          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>render.max_buffer_h</t>
+          <t>time.coast_ticks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>540</v>
+        <v>45</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
+          <t>How long the world keeps running after you stop moving the view. 60 ticks is a second. Set it to 0 and time stops the very instant you do -- which is strictly what rule 11 says, but on a phone it makes the game look frozen between drags.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>time.coast_ticks</t>
+          <t>world.rooms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>How long the world keeps running after you stop moving the view. 0 means time stops the instant you do.</t>
+          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>world.rooms</t>
+          <t>world.room_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rooms</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
+          <t>Smallest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>world.room_min</t>
+          <t>world.room_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1630,18 +1630,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Smallest a room can be, along one side.</t>
+          <t>Largest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>world.room_max</t>
+          <t>world.hall_width</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1650,14 +1650,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Largest a room can be, along one side.</t>
+          <t>How wide the halls between rooms are.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>world.hall_width</t>
+          <t>world.rock_height</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1670,187 +1670,247 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How wide the halls between rooms are.</t>
+          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>world.rock_height</t>
+          <t>camp.bedrolls</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
+          <t>How many bedrolls the crawlers lay out around the fire.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>camp.bedrolls</t>
+          <t>camp.stores</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>stores</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How many bedrolls the crawlers lay out around the fire.</t>
+          <t>How many stores the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>camp.stores</t>
+          <t>camp.windbreaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>stores</t>
+          <t>windbreaks</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How many stores the crawlers put up.</t>
+          <t>How many windbreaks the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>camp.windbreaks</t>
+          <t>camp.site_spread</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>windbreaks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How many windbreaks the crawlers put up.</t>
+          <t>How far from the fire the rest of the camp is laid out.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>camp.site_spread</t>
+          <t>camp.progress_per_success</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How far from the fire the rest of the camp is laid out.</t>
+          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>camp.progress_per_success</t>
+          <t>camp.work_ticks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
+          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>camp.work_ticks</t>
+          <t>render.cutaway_fade</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
+          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>render.cutaway_fade</t>
+          <t>render.cutaway_depth</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
+          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>render.cutaway_depth</t>
+          <t>render.tile_h_low</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
+          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>render.tile_h_high</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>54</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>camera.swing_ms</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>320</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>camera.tilt_ms</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>260</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>How long the view takes to rise to the higher angle and back.</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2061,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>drag to pan  ·  scroll to zoom  ·  hover anything to inspect it</t>
+          <t>drag to pan  ·  scroll to zoom  ·  Q/E turn, R raises the angle  ·  hover to inspect</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2073,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>drag to pan  ·  pinch to zoom  ·  tap anything to inspect it</t>
+          <t>drag to pan  ·  pinch to zoom  ·  buttons turn and raise the view  ·  tap to inspect</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -15,8 +15,11 @@
     <sheet name="tiles" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="attributes" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="skills" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="figure" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="structures" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="bones" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="slots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gear" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="figure" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="structures" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,6 +730,2814 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Helms, hats, hoods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Neck</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Collars, amulets, scarves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Packs, capes, bedrolls, anything carried on the back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Torso</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Armour, coats, shirts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Elbow down: forearms and hands together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mainhand</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mainhand</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The tool or weapon in the right hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Offhand</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Shield, lantern, or a second tool, in the left hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Belts, sashes, tool loops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hips to knees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Feet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Knees down: shins and feet together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>trinket1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trinket 1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A small carried thing. Hangs at the left hip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>trinket2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trinket 2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A small carried thing. Hangs at the right hip.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="78" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>attr</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hood</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hood</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cloth,leather</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>willpower:1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Keeps the drip off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>collar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Collar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>presence:1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A worn strap, buckled at the throat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>leather,store</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>might:1,agility:-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>labouring:4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Everything they own, on their back. Carries more and slows you down: the trade-off is the point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>jerkin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jerkin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>endurance:1,agility:-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Boiled hide. Better than nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Work Gloves</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>labouring:6,tinkering:4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Elbow to fingertip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>spade</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spade</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mainhand</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>iron,wood,tool</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>labouring:10,building:8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>For digging, clearing and, at a push, arguing. Counts as a tool, so it is what makes Building and Labouring possible at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lantern</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>iron,glass,light</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>studying:6,foraging:4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Burns something. Nobody asks what.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>toolbelt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tool Belt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>leather,tool</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>crafting:5,building:4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Loops and a buckle. Also counts as a tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>breeches</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Breeches</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cloth</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>endurance:1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hip to knee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>clambering:8,ranging:6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Knee down. The first thing a crawler buys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>coil</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rope Coil</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>trinket1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>rope</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>clambering:5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Twenty metres, if you believe the seller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>charm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bone Charm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>trinket2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>organic,charm,grim</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>willpower:1,presence:-1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Somebody's knuckle, on a thong.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="78" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>bone</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>ox</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>oy</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>from_m</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>to_m</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>w_top</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>w_bot</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>d_top</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>d_bot</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>#a08a70</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Always drawn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Neck</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>#a08a70</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Torso</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#5c5145</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Wider at the shoulders than the waist -- the taper is what makes a figure read as a person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pelvis</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pelvis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#33302c</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>upperarm_l</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Upper Arm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>shoulder_l</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#5c5145</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>forearm_l</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Forearm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>elbow_l</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#a08a70</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#a08a70</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thigh_l</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Thigh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thigh_l</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>#33302c</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>shin_l</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Shin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>knee_l</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#33302c</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>foot_l</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>foot_l</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#2b2825</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>upperarm_r</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Upper Arm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>shoulder_r</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#5c5145</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>forearm_r</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Forearm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>elbow_r</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>#a08a70</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hand_r</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>hand_r</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>#a08a70</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thigh_r</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Thigh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>thigh_r</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>#33302c</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>shin_r</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>knee_r</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>#33302c</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>foot_r</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>foot_r</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>#2b2825</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hood_v</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hood</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>hood</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>#3a352f</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>collar_v</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Collar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>collar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>#4a4038</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pack_v</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>#5a4a34</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sits behind the chest, which is what the oy offset is for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>jerkin_v</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jerkin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jerkin</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>#6b5335</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>glove_fore_l</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Glove</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>elbow_l</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>#4b3b28</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>glove_hand_l</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Glove</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>#4b3b28</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>breech_l</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Breeches</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>breeches</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>thigh_l</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>#4a4136</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>boot_shin_l</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Boot</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>knee_l</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>#3b2f22</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>boot_foot_l</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Boot</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>foot_l</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>#3b2f22</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>glove_fore_r</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Glove</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>elbow_r</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>#4b3b28</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>glove_hand_r</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Glove</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>hand_r</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>#4b3b28</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>breech_r</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Breeches</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>breeches</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>thigh_r</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>#4a4136</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>boot_shin_r</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Boot</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>knee_r</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>#3b2f22</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>boot_foot_r</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Boot</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>foot_r</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>#3b2f22</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>belt_v</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tool Belt</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>toolbelt</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>#4b3b28</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>spade_haft</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Spade Haft</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mainhand</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>spade</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>hand_r</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>#6b5334</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>spade_blade</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spade Blade</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mainhand</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>spade</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>hand_r</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>#7d8189</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>lantern_v</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>lantern</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>#c98a2e</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>coil_v</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rope Coil</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>trinket1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>coil</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>#8a7a5a</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>charm_v</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bone Charm</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>trinket2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>charm</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>#b3ab92</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -963,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1397,71 +4208,71 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>actor.hat_chance</t>
+          <t>actor.step_ticks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5</v>
+        <v>26</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>How many crawlers turn up already wearing something on their head.</t>
+          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>actor.step_ticks</t>
+          <t>actor.height_m</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26</v>
+        <v>1.625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
+          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>actor.height_m</t>
+          <t>render.zoom_start</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
+          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>render.zoom_start</t>
+          <t>render.zoom_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1470,18 +4281,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
+          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>render.zoom_min</t>
+          <t>render.zoom_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1490,38 +4301,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
+          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>render.zoom_max</t>
+          <t>render.max_buffer_w</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>960</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
+          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>render.max_buffer_w</t>
+          <t>render.max_buffer_h</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>960</v>
+        <v>540</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1530,78 +4341,78 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
+          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>render.max_buffer_h</t>
+          <t>time.coast_ticks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>540</v>
+        <v>45</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
+          <t>How long the world keeps running after you stop moving the view. 60 ticks is a second. Set it to 0 and time stops the very instant you do -- which is strictly what rule 11 says, but on a phone it makes the game look frozen between drags.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>time.coast_ticks</t>
+          <t>world.rooms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>How long the world keeps running after you stop moving the view. 60 ticks is a second. Set it to 0 and time stops the very instant you do -- which is strictly what rule 11 says, but on a phone it makes the game look frozen between drags.</t>
+          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>world.rooms</t>
+          <t>world.room_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rooms</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
+          <t>Smallest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>world.room_min</t>
+          <t>world.room_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1610,18 +4421,18 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Smallest a room can be, along one side.</t>
+          <t>Largest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>world.room_max</t>
+          <t>world.hall_width</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1630,14 +4441,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Largest a room can be, along one side.</t>
+          <t>How wide the halls between rooms are.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>world.hall_width</t>
+          <t>world.rock_height</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1650,198 +4461,198 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How wide the halls between rooms are.</t>
+          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>world.rock_height</t>
+          <t>camp.bedrolls</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
+          <t>How many bedrolls the crawlers lay out around the fire.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>camp.bedrolls</t>
+          <t>camp.stores</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>stores</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How many bedrolls the crawlers lay out around the fire.</t>
+          <t>How many stores the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>camp.stores</t>
+          <t>camp.windbreaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>stores</t>
+          <t>windbreaks</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How many stores the crawlers put up.</t>
+          <t>How many windbreaks the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>camp.windbreaks</t>
+          <t>camp.site_spread</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>windbreaks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How many windbreaks the crawlers put up.</t>
+          <t>How far from the fire the rest of the camp is laid out.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>camp.site_spread</t>
+          <t>camp.progress_per_success</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How far from the fire the rest of the camp is laid out.</t>
+          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>camp.progress_per_success</t>
+          <t>camp.work_ticks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
+          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>camp.work_ticks</t>
+          <t>render.cutaway_fade</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
+          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>render.cutaway_fade</t>
+          <t>render.cutaway_depth</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
+          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>render.cutaway_depth</t>
+          <t>render.tile_h_low</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
+          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>render.tile_h_low</t>
+          <t>render.tile_h_high</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1850,38 +4661,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
+          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>render.tile_h_high</t>
+          <t>camera.swing_ms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>54</v>
+        <v>320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
+          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>camera.swing_ms</t>
+          <t>camera.tilt_ms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1890,27 +4701,287 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
+          <t>How long the view takes to rise to the higher angle and back.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>camera.tilt_ms</t>
+          <t>anim.walk_ticks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>260</v>
+        <v>34</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>How long the view takes to rise to the higher angle and back.</t>
+          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>anim.walk_leg_swing</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>How far the legs swing forward and back while walking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>anim.walk_knee_bend</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>How much the trailing knee folds as the leg comes through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>anim.walk_arm_swing</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>26</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>How far the arms swing, opposite to the legs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>anim.walk_bob</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>How far a crawler rises and falls with each step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>anim.work_ticks</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>40</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>How long one swing of a tool takes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>anim.work_arm_lift</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>78</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>How far the arms come up for a swing of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>anim.work_lean</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>14</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>How far a crawler leans into their work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>anim.idle_ticks</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>150</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>How long one slow breath takes while standing about.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>anim.idle_sway</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>How much a crawler sways while standing about.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>anim.turn_ticks</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>How long a crawler takes to turn to face a new direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>render.light_ambient</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>How lit the darkest face of anything is. Raise it to flatten the lighting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>render.light_diffuse</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>How much brighter a face gets for facing the light.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>actor.gear_chance</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
         </is>
       </c>
     </row>
@@ -2003,7 +5074,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75</v>
+        <v>1.625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2012,7 +5083,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>READ ONLY. The height the figure tab's part measurements are written against. A crawler of a different height has every part scaled by the same ratio.</t>
+          <t>READ ONLY. The height the skeleton and the figure parts are measured against. A crawler of a different height is scaled by the ratio.</t>
         </is>
       </c>
     </row>
@@ -2034,7 +5105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2362,6 +5433,42 @@
       <c r="B27" t="inlineStr">
         <is>
           <t>looking about</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ui.label_gear</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ui.label_effect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ui.label_empty</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nothing</t>
         </is>
       </c>
     </row>
@@ -2376,7 +5483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2789,6 +5896,125 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>Holds off the cold. Crawlers will come to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cured hide. Tough, and it creaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cold, heavy, and it rusts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rope</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rope</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Twisted fibre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sees through, and breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Made for work, not for fighting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gives light in the dark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>charm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>charm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Carried for luck, or for something worse.</t>
         </is>
       </c>
     </row>
@@ -3393,13 +6619,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3420,6 +6648,16 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>needs_tag</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>without</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -3440,7 +6678,11 @@
           <t>might:1,agility:1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Climbing, scrambling, and keeping your feet on ground that does not want you to. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3464,7 +6706,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hauling, digging, clearing ground, and still doing it an hour later. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hauling, digging, clearing ground, and still doing it an hour later. (Every skill is one pair of the six attributes; all fifteen pairs exist.) Bare hands cost 20 points.</t>
         </is>
       </c>
     </row>
@@ -3484,7 +6734,11 @@
           <t>might:1,presence:1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Handling animals, and dragging people out of trouble whether they like it or not. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3508,7 +6762,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raising structures that stay up. Knowing where the weight goes, and being able to put it there. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Raising structures that stay up. Knowing where the weight goes, and being able to put it there. (Every skill is one pair of the six attributes; all fifteen pairs exist.) Needs a tool in hand: without one the job is 30 points harder, which is close to impossible.</t>
         </is>
       </c>
     </row>
@@ -3528,7 +6790,11 @@
           <t>might:1,willpower:1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>The one fifth of the game that is violence. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3550,7 +6816,11 @@
           <t>agility:1,endurance:1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Covering ground: travelling far, moving quietly, getting back again. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3572,7 +6842,11 @@
           <t>agility:1,presence:1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Singing, playing, dancing, and holding a room while you do it. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3596,6 +6870,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Making and mending: tools, clothes, meals, anything that takes hands and a recipe. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
       </c>
@@ -3618,6 +6900,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Locks, traps, and anything fiddly that punishes a shaking hand. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
       </c>
@@ -3638,7 +6928,11 @@
           <t>endurance:1,presence:1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Nursing, feeding, and keeping people upright who would rather lie down. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3660,7 +6954,11 @@
           <t>endurance:1,intellect:1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Hunting, fishing, gathering, and knowing which of it is safe to eat. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3682,7 +6980,11 @@
           <t>endurance:1,willpower:1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Cold, hunger, pain, boredom and the dark. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3704,7 +7006,11 @@
           <t>presence:1,intellect:1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Trading, persuading, and working out what somebody actually wants. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3726,7 +7032,11 @@
           <t>presence:1,willpower:1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Rallying, calming a panic, and holding a group together when it wants to scatter. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3748,7 +7058,11 @@
           <t>intellect:1,willpower:1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Lore, mapmaking, deciphering, and sitting with a problem until it gives. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
@@ -3765,7 +7079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3774,8 +7088,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="78" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3791,30 +7104,25 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>slot</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>colour</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>half_width</t>
+          <t>y</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>from_m</t>
+          <t>z</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>to_m</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -3823,146 +7131,469 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>root</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Legs</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>#33302c</t>
-        </is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Always drawn.</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Between the feet, on the ground. Everything hangs off this, and it is what turns when a crawler changes direction.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>torso</t>
+          <t>hips</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Torso</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>#5c5145</t>
-        </is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Always drawn. The cloth colour, and the widest part of a crawler.</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>#ab977d</t>
-        </is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Always drawn.</t>
-        </is>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hat</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hat</t>
+          <t>Neck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hat</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>#23201d</t>
-        </is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shoulder_l</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Left Shoulder</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.17</v>
       </c>
-      <c r="F5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Only drawn on a crawler wearing one. Keep half_width near the head's or the brim hides the face. Rule 4: if it is on them, it is on screen -- add a row here and it can be worn.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>shoulder_r</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Right Shoulder</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>elbow_l</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Left Elbow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>shoulder_l</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>elbow_r</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Right Elbow</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>shoulder_r</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Left Hand</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>elbow_l</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Where the offhand item is held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hand_r</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>elbow_r</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Where the mainhand item is held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thigh_l</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Left Thigh</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thigh_r</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Right Thigh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hips</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>knee_l</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Left Knee</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>thigh_l</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>knee_r</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Right Knee</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>thigh_r</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>foot_l</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Left Foot</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>knee_l</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>foot_r</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Right Foot</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>knee_r</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -3774,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4348,51 +4348,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>time.coast_ticks</t>
+          <t>world.rooms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>How long the world keeps running after you stop moving the view. 60 ticks is a second. Set it to 0 and time stops the very instant you do -- which is strictly what rule 11 says, but on a phone it makes the game look frozen between drags.</t>
+          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>world.rooms</t>
+          <t>world.room_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rooms</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
+          <t>Smallest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>world.room_min</t>
+          <t>world.room_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4401,18 +4401,18 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Smallest a room can be, along one side.</t>
+          <t>Largest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>world.room_max</t>
+          <t>world.hall_width</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4421,14 +4421,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Largest a room can be, along one side.</t>
+          <t>How wide the halls between rooms are.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>world.hall_width</t>
+          <t>world.rock_height</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -4441,198 +4441,198 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How wide the halls between rooms are.</t>
+          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>world.rock_height</t>
+          <t>camp.bedrolls</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
+          <t>How many bedrolls the crawlers lay out around the fire.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>camp.bedrolls</t>
+          <t>camp.stores</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>stores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How many bedrolls the crawlers lay out around the fire.</t>
+          <t>How many stores the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>camp.stores</t>
+          <t>camp.windbreaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>stores</t>
+          <t>windbreaks</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How many stores the crawlers put up.</t>
+          <t>How many windbreaks the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>camp.windbreaks</t>
+          <t>camp.site_spread</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>windbreaks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How many windbreaks the crawlers put up.</t>
+          <t>How far from the fire the rest of the camp is laid out.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>camp.site_spread</t>
+          <t>camp.progress_per_success</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How far from the fire the rest of the camp is laid out.</t>
+          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>camp.progress_per_success</t>
+          <t>camp.work_ticks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
+          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>camp.work_ticks</t>
+          <t>render.cutaway_fade</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
+          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>render.cutaway_fade</t>
+          <t>render.cutaway_depth</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
+          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>render.cutaway_depth</t>
+          <t>render.tile_h_low</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
+          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>render.tile_h_low</t>
+          <t>render.tile_h_high</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4641,38 +4641,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
+          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>render.tile_h_high</t>
+          <t>camera.swing_ms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>54</v>
+        <v>320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
+          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>camera.swing_ms</t>
+          <t>camera.tilt_ms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4681,58 +4681,58 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
+          <t>How long the view takes to rise to the higher angle and back.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>camera.tilt_ms</t>
+          <t>anim.walk_ticks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>260</v>
+        <v>34</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>How long the view takes to rise to the higher angle and back.</t>
+          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>anim.walk_ticks</t>
+          <t>anim.walk_leg_swing</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
+          <t>How far the legs swing forward and back while walking.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>anim.walk_leg_swing</t>
+          <t>anim.walk_knee_bend</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -4741,18 +4741,18 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>How far the legs swing forward and back while walking.</t>
+          <t>How much the trailing knee folds as the leg comes through.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>anim.walk_knee_bend</t>
+          <t>anim.walk_arm_swing</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -4761,78 +4761,78 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>How much the trailing knee folds as the leg comes through.</t>
+          <t>How far the arms swing, opposite to the legs.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>anim.walk_arm_swing</t>
+          <t>anim.walk_bob</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26</v>
+        <v>0.035</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>How far the arms swing, opposite to the legs.</t>
+          <t>How far a crawler rises and falls with each step.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>anim.walk_bob</t>
+          <t>anim.work_ticks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.035</v>
+        <v>40</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>How far a crawler rises and falls with each step.</t>
+          <t>How long one swing of a tool takes.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>anim.work_ticks</t>
+          <t>anim.work_arm_lift</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How long one swing of a tool takes.</t>
+          <t>How far the arms come up for a swing of work.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>anim.work_arm_lift</t>
+          <t>anim.work_lean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4841,98 +4841,98 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How far the arms come up for a swing of work.</t>
+          <t>How far a crawler leans into their work.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>anim.work_lean</t>
+          <t>anim.idle_ticks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How far a crawler leans into their work.</t>
+          <t>How long one slow breath takes while standing about.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>anim.idle_ticks</t>
+          <t>anim.idle_sway</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>150</v>
+        <v>4.5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How long one slow breath takes while standing about.</t>
+          <t>How much a crawler sways while standing about.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>anim.idle_sway</t>
+          <t>anim.turn_ticks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How much a crawler sways while standing about.</t>
+          <t>How long a crawler takes to turn to face a new direction.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>anim.turn_ticks</t>
+          <t>render.light_ambient</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>0.46</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How long a crawler takes to turn to face a new direction.</t>
+          <t>How lit the darkest face of anything is. Raise it to flatten the lighting.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>render.light_ambient</t>
+          <t>render.light_diffuse</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4941,45 +4941,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How lit the darkest face of anything is. Raise it to flatten the lighting.</t>
+          <t>How much brighter a face gets for facing the light.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>render.light_diffuse</t>
+          <t>actor.gear_chance</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
-        <is>
-          <t>How much brighter a face gets for facing the light.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>actor.gear_chance</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
         <is>
           <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
         </is>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -17,9 +17,10 @@
     <sheet name="skills" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="bones" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="slots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="gear" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="figure" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="structures" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="speeds" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="gear" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="figure" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="structures" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -970,6 +971,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1×</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Real time. One tick is a sixtieth of a second. The first row is always normal speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2×</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Twice as fast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>faster</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4×</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Four times. About right for watching a camp go up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fastest</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8×</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Eight times. Add a row here for a faster one, or delete one you never use.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1424,7 +1547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3532,7 +3655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3774,7 +3897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4962,6 +5085,26 @@
       <c r="D59" t="inlineStr">
         <is>
           <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>time.max_steps_per_frame</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>64</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The most the world is allowed to advance in a single drawn frame. Stops a slow machine, or a tab left in the background, from lurching forward all at once.</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5112,7 +5255,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>drag to pan  ·  scroll to zoom  ·  Q/E turn, R raises the angle  ·  hover to inspect</t>
+          <t>drag to pan  ·  scroll to zoom  ·  Q/E turn, R raises  ·  space pauses, , and . change speed</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5267,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>drag to pan  ·  pinch to zoom  ·  buttons turn and raise the view  ·  tap to inspect</t>
+          <t>drag to pan  ·  pinch to zoom  ·  the buttons turn, raise, pause and change speed</t>
         </is>
       </c>
     </row>
@@ -5449,6 +5592,66 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ui.label_paused</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ui.label_speed</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ui.button_pause</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pause (space)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ui.button_slower</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>slower (,)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ui.button_faster</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>faster (.)</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -3897,7 +3897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5105,6 +5105,26 @@
       <c r="D60" t="inlineStr">
         <is>
           <t>The most the world is allowed to advance in a single drawn frame. Stops a slow machine, or a tab left in the background, from lurching forward all at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>render.outline_width</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>How thick the highlight ring around a selected thing is drawn. It is drawn UNDER the thing and half of it is covered, so 2 here shows as a 1 pixel line around the silhouette.</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5652,6 +5672,78 @@
       <c r="B35" t="inlineStr">
         <is>
           <t>faster (.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ui.colour_outline</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>#ffe9a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ui.label_inspect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>click to inspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ui.label_close</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ui.section_attributes</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ui.section_skills</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ui.section_gear</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>gear</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -1553,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1570,7 +1570,12 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="78" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="78" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1646,6 +1651,31 @@
       </c>
       <c r="O1" s="3" t="inlineStr">
         <is>
+          <t>sides</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>rings</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>bulge</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>cap_top</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>cap_bot</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1701,9 +1731,24 @@
       <c r="N2" t="n">
         <v>0.08</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Always drawn.</t>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Always drawn. Eight sides and a domed top: at 52 pixels tall the silhouette is most of what you read.</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1803,22 @@
       <c r="N3" t="n">
         <v>0.048</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1811,9 +1871,24 @@
       <c r="N4" t="n">
         <v>0.082</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Wider at the shoulders than the waist -- the taper is what makes a figure read as a person.</t>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Always drawn. Wider at the shoulders, pinched at the waist, and swelling slightly in between -- that is what makes a figure read as a body.</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1943,22 @@
       <c r="N5" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1921,7 +2011,22 @@
       <c r="N6" t="n">
         <v>0.044</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1974,7 +2079,22 @@
       <c r="N7" t="n">
         <v>0.038</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2027,7 +2147,22 @@
       <c r="N8" t="n">
         <v>0.03</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2080,7 +2215,22 @@
       <c r="N9" t="n">
         <v>0.062</v>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2133,7 +2283,22 @@
       <c r="N10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2186,7 +2351,22 @@
       <c r="N11" t="n">
         <v>0.095</v>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2239,7 +2419,22 @@
       <c r="N12" t="n">
         <v>0.044</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2292,7 +2487,22 @@
       <c r="N13" t="n">
         <v>0.038</v>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2345,7 +2555,22 @@
       <c r="N14" t="n">
         <v>0.03</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2398,7 +2623,22 @@
       <c r="N15" t="n">
         <v>0.062</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2451,7 +2691,22 @@
       <c r="N16" t="n">
         <v>0.05</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2504,7 +2759,22 @@
       <c r="N17" t="n">
         <v>0.095</v>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2561,7 +2831,22 @@
       <c r="N18" t="n">
         <v>0.098</v>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2607,18 +2892,33 @@
         <v>0.04</v>
       </c>
       <c r="K19" t="n">
-        <v>0.068</v>
+        <v>0.076</v>
       </c>
       <c r="L19" t="n">
-        <v>0.066</v>
+        <v>0.074</v>
       </c>
       <c r="M19" t="n">
-        <v>0.068</v>
+        <v>0.076</v>
       </c>
       <c r="N19" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
+        <v>0.074</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2675,7 +2975,22 @@
       <c r="N20" t="n">
         <v>0.062</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>Sits behind the chest, which is what the oy offset is for.</t>
         </is>
@@ -2736,7 +3051,22 @@
       <c r="N21" t="n">
         <v>0.093</v>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2793,7 +3123,22 @@
       <c r="N22" t="n">
         <v>0.046</v>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2850,7 +3195,22 @@
       <c r="N23" t="n">
         <v>0.038</v>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2907,7 +3267,22 @@
       <c r="N24" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2964,7 +3339,22 @@
       <c r="N25" t="n">
         <v>0.058</v>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3021,7 +3411,22 @@
       <c r="N26" t="n">
         <v>0.105</v>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3078,7 +3483,22 @@
       <c r="N27" t="n">
         <v>0.046</v>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3135,7 +3555,22 @@
       <c r="N28" t="n">
         <v>0.038</v>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3192,7 +3627,22 @@
       <c r="N29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3249,7 +3699,22 @@
       <c r="N30" t="n">
         <v>0.058</v>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3306,7 +3771,22 @@
       <c r="N31" t="n">
         <v>0.105</v>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3363,7 +3843,22 @@
       <c r="N32" t="n">
         <v>0.094</v>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3409,18 +3904,33 @@
         <v>0.46</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M33" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3466,18 +3976,33 @@
         <v>-0.2</v>
       </c>
       <c r="K34" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="M34" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="N34" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>0.024</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3523,18 +4048,33 @@
         <v>-0.06</v>
       </c>
       <c r="K35" t="n">
-        <v>0.048</v>
+        <v>0.078</v>
       </c>
       <c r="L35" t="n">
-        <v>0.044</v>
+        <v>0.0702</v>
       </c>
       <c r="M35" t="n">
-        <v>0.048</v>
+        <v>0.078</v>
       </c>
       <c r="N35" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
+        <v>0.0702</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3580,18 +4120,37 @@
         <v>0.04</v>
       </c>
       <c r="K36" t="n">
-        <v>0.048</v>
+        <v>0.09</v>
       </c>
       <c r="L36" t="n">
-        <v>0.044</v>
+        <v>0.081</v>
       </c>
       <c r="M36" t="n">
-        <v>0.048</v>
+        <v>0.09</v>
       </c>
       <c r="N36" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
+        <v>0.081</v>
+      </c>
+      <c r="O36" t="n">
+        <v>6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Drawn larger than life so the coil reads at 32 pixels to the metre.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3637,18 +4196,37 @@
         <v>0.02</v>
       </c>
       <c r="K37" t="n">
-        <v>0.026</v>
+        <v>0.062</v>
       </c>
       <c r="L37" t="n">
-        <v>0.024</v>
+        <v>0.0558</v>
       </c>
       <c r="M37" t="n">
-        <v>0.026</v>
+        <v>0.062</v>
       </c>
       <c r="N37" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
+        <v>0.0558</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Drawn larger than life: a true-scale knuckle bone would be under a pixel wide, and rule 4 says it has to be visible.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3897,7 +4475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5125,6 +5703,122 @@
       <c r="D61" t="inlineStr">
         <is>
           <t>How thick the highlight ring around a selected thing is drawn. It is drawn UNDER the thing and half of it is covered, so 2 here shows as a 1 pixel line around the silhouette.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>texture.floor_px</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>16</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>How big one square of the ground's grain is. The grain repeats every this many pixels across the floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>texture.fine_px</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>How big the grain is on crawlers and on anything built. Smaller than the floor's, because a face is only about eight pixels across.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>texture.strength</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>How strongly the grain darkens and lightens what is underneath. 0 turns texture off entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>texture.speck</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>How much of the grain is hard specks of grit and rust rather than soft mottling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>texture.seed</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Which grain gets generated. Change it for a different pattern of grit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>render.min_face_px</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>labouring:4</t>
+          <t>labouring:1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>labouring:6,tinkering:4</t>
+          <t>labouring:2,tinkering:1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1335,7 +1335,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>labouring:10,building:8</t>
+          <t>labouring:3,building:3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>studying:6,foraging:4</t>
+          <t>studying:2,foraging:1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>crafting:5,building:4</t>
+          <t>crafting:2,building:1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1467,7 +1467,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>clambering:8,ranging:6</t>
+          <t>clambering:2,ranging:2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>clambering:5</t>
+          <t>clambering:1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>How much a natural attribute is worth in a roll. A 10 in the attribute is worth 30 with this at 3.</t>
+          <t>How much a natural attribute is worth in a roll. At 1, an attribute of 4 is worth 4 -- the number on the sheet is the number in the roll.</t>
         </is>
       </c>
     </row>
@@ -4722,18 +4722,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>How much practice is worth in a roll. At 1, a skill of 100 is worth 100 -- practice eventually outweighs talent.</t>
+          <t>How much practice is worth in a roll. At 1, a skill of 3 is worth 3.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>roll.noise_spread</t>
+          <t>skill.cap</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4742,18 +4742,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>How much luck swings a single attempt, either way. Lower makes the better character win more reliably.</t>
+          <t>The most practice any one skill can hold. Six, the same scale as an attribute.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>skill.cap</t>
+          <t>learn.gain_on_failure</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4762,18 +4762,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The most practice any one skill can hold.</t>
+          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a crawler learns. Ten failures is a tenth of the way to mastery.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>learn.gain_on_failure</t>
+          <t>learn.gain_on_success</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4782,18 +4782,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a character learns.</t>
+          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>learn.gain_on_success</t>
+          <t>learn.near_miss_bonus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4802,18 +4802,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
+          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>learn.near_miss_bonus</t>
+          <t>learn.near_miss_margin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4822,58 +4822,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
+          <t>How close a failure has to be to count as only just missing. Two, on a scale where a whole roll is about a dozen.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>learn.near_miss_margin</t>
+          <t>actor.count</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>people</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>How close a failure has to be to count as only just missing.</t>
+          <t>How many crawlers turn up in the labyrinth.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>actor.count</t>
+          <t>actor.attribute_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>How many crawlers turn up in the labyrinth.</t>
+          <t>Lowest a natural attribute can be. One to six, like a die: 3 and 4 are ordinary, 1 and 6 are remarkable.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>actor.attribute_min</t>
+          <t>actor.attribute_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4882,78 +4882,78 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lowest a natural attribute can be rolled at. Ordinary people sit near 10.</t>
+          <t>Highest a natural attribute can be.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>actor.attribute_max</t>
+          <t>actor.step_ticks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Highest a natural attribute can be rolled at.</t>
+          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>actor.step_ticks</t>
+          <t>actor.height_m</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>1.625</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
+          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>actor.height_m</t>
+          <t>render.zoom_start</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
+          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>render.zoom_start</t>
+          <t>render.zoom_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4962,18 +4962,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
+          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>render.zoom_min</t>
+          <t>render.zoom_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4982,38 +4982,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
+          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>render.zoom_max</t>
+          <t>render.max_buffer_w</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>960</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
+          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>render.max_buffer_w</t>
+          <t>render.max_buffer_h</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>960</v>
+        <v>540</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5022,58 +5022,58 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
+          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>render.max_buffer_h</t>
+          <t>world.rooms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>540</v>
+        <v>9</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
+          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>world.rooms</t>
+          <t>world.room_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rooms</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
+          <t>Smallest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>world.room_min</t>
+          <t>world.room_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5082,18 +5082,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Smallest a room can be, along one side.</t>
+          <t>Largest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>world.room_max</t>
+          <t>world.hall_width</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5102,14 +5102,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Largest a room can be, along one side.</t>
+          <t>How wide the halls between rooms are.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>world.hall_width</t>
+          <t>world.rock_height</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5122,198 +5122,198 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How wide the halls between rooms are.</t>
+          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>world.rock_height</t>
+          <t>camp.bedrolls</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
+          <t>How many bedrolls the crawlers lay out around the fire.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>camp.bedrolls</t>
+          <t>camp.stores</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>stores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How many bedrolls the crawlers lay out around the fire.</t>
+          <t>How many stores the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>camp.stores</t>
+          <t>camp.windbreaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>stores</t>
+          <t>windbreaks</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How many stores the crawlers put up.</t>
+          <t>How many windbreaks the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>camp.windbreaks</t>
+          <t>camp.site_spread</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>windbreaks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How many windbreaks the crawlers put up.</t>
+          <t>How far from the fire the rest of the camp is laid out.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>camp.site_spread</t>
+          <t>camp.progress_per_success</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How far from the fire the rest of the camp is laid out.</t>
+          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>camp.progress_per_success</t>
+          <t>camp.work_ticks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
+          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>camp.work_ticks</t>
+          <t>render.cutaway_fade</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
+          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>render.cutaway_fade</t>
+          <t>render.cutaway_depth</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
+          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>render.cutaway_depth</t>
+          <t>render.tile_h_low</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
+          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>render.tile_h_low</t>
+          <t>render.tile_h_high</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5322,38 +5322,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
+          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>render.tile_h_high</t>
+          <t>camera.swing_ms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54</v>
+        <v>320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
+          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>camera.swing_ms</t>
+          <t>camera.tilt_ms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5362,58 +5362,58 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
+          <t>How long the view takes to rise to the higher angle and back.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>camera.tilt_ms</t>
+          <t>anim.walk_ticks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>260</v>
+        <v>34</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>How long the view takes to rise to the higher angle and back.</t>
+          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>anim.walk_ticks</t>
+          <t>anim.walk_leg_swing</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
+          <t>How far the legs swing forward and back while walking.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>anim.walk_leg_swing</t>
+          <t>anim.walk_knee_bend</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5422,18 +5422,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>How far the legs swing forward and back while walking.</t>
+          <t>How much the trailing knee folds as the leg comes through.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>anim.walk_knee_bend</t>
+          <t>anim.walk_arm_swing</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5442,78 +5442,78 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>How much the trailing knee folds as the leg comes through.</t>
+          <t>How far the arms swing, opposite to the legs.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>anim.walk_arm_swing</t>
+          <t>anim.walk_bob</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26</v>
+        <v>0.035</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>How far the arms swing, opposite to the legs.</t>
+          <t>How far a crawler rises and falls with each step.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>anim.walk_bob</t>
+          <t>anim.work_ticks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.035</v>
+        <v>40</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>How far a crawler rises and falls with each step.</t>
+          <t>How long one swing of a tool takes.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>anim.work_ticks</t>
+          <t>anim.work_arm_lift</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>How long one swing of a tool takes.</t>
+          <t>How far the arms come up for a swing of work.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>anim.work_arm_lift</t>
+          <t>anim.work_lean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5522,98 +5522,98 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How far the arms come up for a swing of work.</t>
+          <t>How far a crawler leans into their work.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>anim.work_lean</t>
+          <t>anim.idle_ticks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How far a crawler leans into their work.</t>
+          <t>How long one slow breath takes while standing about.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>anim.idle_ticks</t>
+          <t>anim.idle_sway</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>150</v>
+        <v>4.5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How long one slow breath takes while standing about.</t>
+          <t>How much a crawler sways while standing about.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>anim.idle_sway</t>
+          <t>anim.turn_ticks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How much a crawler sways while standing about.</t>
+          <t>How long a crawler takes to turn to face a new direction.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>anim.turn_ticks</t>
+          <t>render.light_ambient</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8</v>
+        <v>0.46</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How long a crawler takes to turn to face a new direction.</t>
+          <t>How lit the darkest face of anything is. Raise it to flatten the lighting.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>render.light_ambient</t>
+          <t>render.light_diffuse</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5622,78 +5622,78 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How lit the darkest face of anything is. Raise it to flatten the lighting.</t>
+          <t>How much brighter a face gets for facing the light.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>render.light_diffuse</t>
+          <t>actor.gear_chance</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How much brighter a face gets for facing the light.</t>
+          <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>actor.gear_chance</t>
+          <t>time.max_steps_per_frame</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.55</v>
+        <v>64</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
+          <t>The most the world is allowed to advance in a single drawn frame. Stops a slow machine, or a tab left in the background, from lurching forward all at once.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>time.max_steps_per_frame</t>
+          <t>render.outline_width</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>The most the world is allowed to advance in a single drawn frame. Stops a slow machine, or a tab left in the background, from lurching forward all at once.</t>
+          <t>How thick the highlight ring around a selected thing is drawn. It is drawn UNDER the thing and half of it is covered, so 2 here shows as a 1 pixel line around the silhouette.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>render.outline_width</t>
+          <t>texture.floor_px</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5702,18 +5702,18 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How thick the highlight ring around a selected thing is drawn. It is drawn UNDER the thing and half of it is covered, so 2 here shows as a 1 pixel line around the silhouette.</t>
+          <t>How big one square of the ground's grain is. The grain repeats every this many pixels across the floor.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>texture.floor_px</t>
+          <t>texture.fine_px</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5722,38 +5722,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>How big one square of the ground's grain is. The grain repeats every this many pixels across the floor.</t>
+          <t>How big the grain is on crawlers and on anything built. Smaller than the floor's, because a face is only about eight pixels across.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>texture.fine_px</t>
+          <t>texture.strength</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8</v>
+        <v>0.17</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>How big the grain is on crawlers and on anything built. Smaller than the floor's, because a face is only about eight pixels across.</t>
+          <t>How strongly the grain darkens and lightens what is underneath. 0 turns texture off entirely.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>texture.strength</t>
+          <t>texture.speck</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.17</v>
+        <v>0.055</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5762,63 +5762,83 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>How strongly the grain darkens and lightens what is underneath. 0 turns texture off entirely.</t>
+          <t>How much of the grain is hard specks of grit and rust rather than soft mottling.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>texture.speck</t>
+          <t>texture.seed</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>How much of the grain is hard specks of grit and rust rather than soft mottling.</t>
+          <t>Which grain gets generated. Change it for a different pattern of grit.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>texture.seed</t>
+          <t>render.min_face_px</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
-      </c>
-      <c r="C66" t="inlineStr"/>
+        <v>0.28</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Which grain gets generated. Change it for a different pattern of grit.</t>
+          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>render.min_face_px</t>
+          <t>roll.dice</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.28</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
+          <t>How many dice are thrown for an attempt. Two gives a bell: middling results are common, extremes are rare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>roll.die_faces</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>faces</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>How many faces each die has.</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6438,6 +6458,18 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>gear</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ui.label_lastroll</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>last roll</t>
         </is>
       </c>
     </row>
@@ -7091,10 +7123,10 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
         <v>8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7134,10 +7166,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7177,10 +7209,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7220,10 +7252,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7263,10 +7295,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7306,10 +7338,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7349,10 +7381,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7392,10 +7424,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="H9" t="n">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7679,11 +7711,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hauling, digging, clearing ground, and still doing it an hour later. (Every skill is one pair of the six attributes; all fifteen pairs exist.) Bare hands cost 20 points.</t>
+          <t>Hauling, digging, clearing ground, and still doing it an hour later. (Every skill is one pair of the six attributes; all fifteen pairs exist.) Bare hands cost 4.</t>
         </is>
       </c>
     </row>
@@ -7735,11 +7767,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-30</v>
+        <v>-6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raising structures that stay up. Knowing where the weight goes, and being able to put it there. (Every skill is one pair of the six attributes; all fifteen pairs exist.) Needs a tool in hand: without one the job is 30 points harder, which is close to impossible.</t>
+          <t>Raising structures that stay up. Knowing where the weight goes, and being able to put it there. (Every skill is one pair of the six attributes; all fifteen pairs exist.) Needs a tool in hand: without one the job is 6 points harder, which on a scale of about a dozen is close to impossible.</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7875,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7873,7 +7905,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -1093,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1102,7 +1102,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="78" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1138,6 +1139,11 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1169,7 +1175,10 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Keeps the drip off.</t>
         </is>
@@ -1202,7 +1211,10 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>A worn strap, buckled at the throat.</t>
         </is>
@@ -1239,7 +1251,10 @@
           <t>labouring:1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Everything they own, on their back. Carries more and slows you down: the trade-off is the point.</t>
         </is>
@@ -1272,7 +1287,10 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Boiled hide. Better than nothing.</t>
         </is>
@@ -1305,7 +1323,10 @@
           <t>labouring:2,tinkering:1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Elbow to fingertip.</t>
         </is>
@@ -1338,7 +1359,10 @@
           <t>labouring:3,building:3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>For digging, clearing and, at a push, arguing. Counts as a tool, so it is what makes Building and Labouring possible at all.</t>
         </is>
@@ -1371,7 +1395,10 @@
           <t>studying:2,foraging:1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Burns something. Nobody asks what.</t>
         </is>
@@ -1404,7 +1431,10 @@
           <t>crafting:2,building:1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Loops and a buckle. Also counts as a tool.</t>
         </is>
@@ -1437,7 +1467,10 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Hip to knee.</t>
         </is>
@@ -1470,7 +1503,10 @@
           <t>clambering:2,ranging:2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Knee down. The first thing a crawler buys.</t>
         </is>
@@ -1503,7 +1539,10 @@
           <t>clambering:1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Twenty metres, if you believe the seller.</t>
         </is>
@@ -1536,9 +1575,80 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Somebody's knuckle, on a thong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>torch</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Torch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>wood,fire,light</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Burns bright and burns out. The most light anybody carries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>candle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Candle</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fire,light</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>studying:1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Barely enough to read by, and it does not free a hand.</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1575,7 +1685,8 @@
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="78" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="78" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1676,6 +1787,11 @@
       </c>
       <c r="T1" s="3" t="inlineStr">
         <is>
+          <t>glow</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1746,7 +1862,10 @@
       <c r="S2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>Always drawn. Eight sides and a domed top: at 52 pixels tall the silhouette is most of what you read.</t>
         </is>
@@ -1818,7 +1937,10 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1886,7 +2008,10 @@
       <c r="S4" t="n">
         <v>0.12</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Always drawn. Wider at the shoulders, pinched at the waist, and swelling slightly in between -- that is what makes a figure read as a body.</t>
         </is>
@@ -1958,7 +2083,10 @@
       <c r="S5" t="n">
         <v>0.1</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2026,7 +2154,10 @@
       <c r="S6" t="n">
         <v>0.18</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2094,7 +2225,10 @@
       <c r="S7" t="n">
         <v>0.2</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2162,7 +2296,10 @@
       <c r="S8" t="n">
         <v>0.3</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2230,7 +2367,10 @@
       <c r="S9" t="n">
         <v>0.1</v>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2298,7 +2438,10 @@
       <c r="S10" t="n">
         <v>0.18</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2366,7 +2509,10 @@
       <c r="S11" t="n">
         <v>0.1</v>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2434,7 +2580,10 @@
       <c r="S12" t="n">
         <v>0.18</v>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2502,7 +2651,10 @@
       <c r="S13" t="n">
         <v>0.2</v>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2570,7 +2722,10 @@
       <c r="S14" t="n">
         <v>0.3</v>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2638,7 +2793,10 @@
       <c r="S15" t="n">
         <v>0.1</v>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2706,7 +2864,10 @@
       <c r="S16" t="n">
         <v>0.18</v>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2774,7 +2935,10 @@
       <c r="S17" t="n">
         <v>0.1</v>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2846,7 +3010,10 @@
       <c r="S18" t="n">
         <v>0.1</v>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2918,7 +3085,10 @@
       <c r="S19" t="n">
         <v>0.05</v>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2990,7 +3160,10 @@
       <c r="S20" t="n">
         <v>0.14</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>Sits behind the chest, which is what the oy offset is for.</t>
         </is>
@@ -3066,7 +3239,10 @@
       <c r="S21" t="n">
         <v>0.1</v>
       </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3138,7 +3314,10 @@
       <c r="S22" t="n">
         <v>0.18</v>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3210,7 +3389,10 @@
       <c r="S23" t="n">
         <v>0.28</v>
       </c>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3282,7 +3464,10 @@
       <c r="S24" t="n">
         <v>0.08</v>
       </c>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3354,7 +3539,10 @@
       <c r="S25" t="n">
         <v>0.14</v>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3426,7 +3614,10 @@
       <c r="S26" t="n">
         <v>0.08</v>
       </c>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3498,7 +3689,10 @@
       <c r="S27" t="n">
         <v>0.18</v>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3570,7 +3764,10 @@
       <c r="S28" t="n">
         <v>0.28</v>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3642,7 +3839,10 @@
       <c r="S29" t="n">
         <v>0.08</v>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3714,7 +3914,10 @@
       <c r="S30" t="n">
         <v>0.14</v>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3786,7 +3989,10 @@
       <c r="S31" t="n">
         <v>0.08</v>
       </c>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3858,7 +4064,10 @@
       <c r="S32" t="n">
         <v>0</v>
       </c>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3930,7 +4139,10 @@
       <c r="S33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4002,7 +4214,10 @@
       <c r="S34" t="n">
         <v>0</v>
       </c>
-      <c r="T34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4074,7 +4289,10 @@
       <c r="S35" t="n">
         <v>0.12</v>
       </c>
-      <c r="T35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4146,7 +4364,10 @@
       <c r="S36" t="n">
         <v>0.18</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr">
         <is>
           <t>Drawn larger than life so the coil reads at 32 pixels to the metre.</t>
         </is>
@@ -4222,11 +4443,318 @@
       <c r="S37" t="n">
         <v>0.3</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>Drawn larger than life: a true-scale knuckle bone would be under a pixel wide, and rule 4 says it has to be visible.</t>
         </is>
       </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>torch_haft</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Torch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>torch</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>#4a3826</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>torch_flame</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Torch Flame</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>torch</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>#e8923a</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O39" t="n">
+        <v>6</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>The lit end. glow 1 means it is never darkened by the room, because it IS the light.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>candle_v</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Candle</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>candle</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>#d8cfae</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="O40" t="n">
+        <v>5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>candle_flame</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Candle Flame</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>offhand</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>candle</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>hand_l</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>#f0b055</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="O41" t="n">
+        <v>5</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4239,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4250,7 +4778,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="78" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4296,6 +4825,11 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -4335,9 +4869,12 @@
       <c r="H2" t="n">
         <v>15</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The heart of a camp. Everything else is laid out around it.</t>
+      <c r="I2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The heart of a camp, and the only thing that lights a room. Everything else is laid out around it.</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4913,10 @@
       <c r="H3" t="n">
         <v>11</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Somewhere to sleep. The easiest thing in a camp to put up.</t>
         </is>
@@ -4417,7 +4957,10 @@
       <c r="H4" t="n">
         <v>13</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Keeps supplies off the wet floor.</t>
         </is>
@@ -4458,7 +5001,10 @@
       <c r="H5" t="n">
         <v>17</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>The hardest thing in a starting camp, and the one that makes it feel like one.</t>
         </is>
@@ -4475,7 +5021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5593,7 +6139,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5602,7 +6148,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How lit the darkest face of anything is. Raise it to flatten the lighting.</t>
+          <t>How lit the darkest FACE of something is, once the lamp has reached it. This is the shape of a thing, not how dark the room is -- that is light.ambient.</t>
         </is>
       </c>
     </row>
@@ -5613,7 +6159,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5839,6 +6385,86 @@
       <c r="D68" t="inlineStr">
         <is>
           <t>How many faces each die has.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>light.ambient</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>How much you can see where nothing is lighting the way. Very low: the labyrinth is dark, and light is something you carry into it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>light.warmth</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>How much a lit thing goes orange rather than just brighter. 0 is cold light, 1 is firelight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>light.steps</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>How many levels of brightness there are between dark and fully lit. Few levels look painted; many look smooth and cost more to draw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>light.falloff</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>How sharply light dies with distance. Above 1 keeps the bright part close to the source.</t>
         </is>
       </c>
     </row>
@@ -7123,10 +7749,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7166,10 +7792,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7209,10 +7835,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7252,10 +7878,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7295,10 +7921,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7338,10 +7964,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7381,10 +8007,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -5021,7 +5021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6465,6 +6465,46 @@
       <c r="D72" t="inlineStr">
         <is>
           <t>How sharply light dies with distance. Above 1 keeps the bright part close to the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>anim.step_ticks</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>22</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>camera.follow</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0 or 1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7096,6 +7136,18 @@
       <c r="B42" t="inlineStr">
         <is>
           <t>last roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ui.label_following</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>following</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -21,6 +21,7 @@
     <sheet name="gear" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="figure" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="structures" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="words" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5015,13 +5016,3033 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>speckle</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>chapel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chapel</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>worked,sacred</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>platform:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A raised altar end and a short colonnade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cathedral</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>worked,sacred,pillared</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pit:1,pillars:3,platform:1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A sunken nave, columns down both sides, a raised apse. Wants a big room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>shrine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Shrine</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>worked,sacred</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>platform:1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>One raised step with something on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ossuary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ossuary</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>worked,grim</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Shelves of bone cut into the levels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mausoleum</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mausoleum</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>worked,sacred,grim</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>platform:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>crypt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Crypt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>worked,grim</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pit:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sunk below the floor it was built under.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cistern</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cistern</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>worked,storage</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pit:2,pillars:2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A deep tank. Usually wet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bathhouse</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bathhouse</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pit:1,terrace:2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Well</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pit:2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>barracks</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Barracks</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>worked,dwelling,martial</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>armoury</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Armoury</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>worked,storage,martial</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>platform:1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>guardroom</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Guardroom</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>worked,martial</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>platform:1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gaol</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gaol</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>worked,captivity</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pit:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>oubliette</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oubliette</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>worked,captivity,grim</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pit:2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>A hole they dropped people into.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>forge</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>worked,industry</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>platform:1,rubble:1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Foundry</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>worked,industry</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pit:1,platform:1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>workshop</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>worked,industry</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>kiln</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kiln</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>worked,industry</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>platform:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>granary</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Granary</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>worked,storage</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pit:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>larder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Larder</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>worked,storage</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>kitchen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>worked,industry</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>platform:1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>brewery</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brewery</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>worked,industry</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pit:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ring:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>slave_market</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Slave Market</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>worked,captivity,profane</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ring:1,pillars:2,platform:1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>counting_house</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Counting House</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>worked,storage</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>worked,storage</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pillars:3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>worked,learning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>terrace:3,pillars:2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>scriptorium</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Scriptorium</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>worked,learning</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>platform:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>observatory</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Observatory</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>worked,learning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>platform:2,ring:1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>arena</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>worked,martial</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>pit:2,ring:1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>rubble</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>menagerie</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Menagerie</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>worked,captivity</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>pit:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kennels</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>worked,captivity</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dormitory</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dormitory</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>worked,dwelling</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>refectory</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Refectory</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>worked,dwelling</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>pillars:2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>infirmary</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Infirmary</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>worked,dwelling</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mine</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>rubble:2,terrace:2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>rubble</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>quarry</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarry</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>terrace:3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>rubble</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gallery</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gallery</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>terrace:2,pillars:2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>garden</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>organic</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>terrace:2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>packed_earth</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>hatchery</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hatchery</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>organic,infested</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>pit:1,platform:1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>throne_room</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Throne Room</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>worked,gilded</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>platform:2,pillars:3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Wants a big room. Everything points at one raised seat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gatehouse</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gatehouse</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>worked,martial</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>platform:1,pillars:2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>stone_floor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>flooded</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Flooded</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>flooded,damp</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>water:1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Fills the lowest ground with standing water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>drowned</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Drowned</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>flooded,damp,grim</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>water:2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>frozen</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>frozen,dry</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>burnt</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Burnt</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>9</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>burnt,dry</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>rubble:1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>scorched</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Scorched</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>burnt,dry</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>collapsed</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Collapsed</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>collapsed,unstable</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>rubble:3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>rubble</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ruined</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ruined</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>collapsed,abandoned</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>rubble:2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>rubble</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>shattered</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Shattered</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>collapsed,unstable</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>rubble:2,terrace:2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>buried</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Buried</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>buried,collapsed</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>rubble:2,platform:1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>abandoned</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Abandoned</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>16</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>abandoned</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>forgotten</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Forgotten</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>abandoned,silent</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>forsaken</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Forsaken</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>abandoned,grim</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>haunted</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Haunted</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>haunted,grim</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>weeping</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Weeping</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>haunted,damp</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>water:1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Silent</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cursed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cursed</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>cursed,grim</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>desecrated</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Desecrated</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>profane,grim</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>rubble:1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>overgrown</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Overgrown</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>overgrown,organic,damp</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>mossy</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mossy</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>overgrown,damp</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fungal</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>overgrown,organic,damp</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>moss_stone</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>shallow_water</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>infested</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Infested</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>infested</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>plundered</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Plundered</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>abandoned</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>rubble:1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sealed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>silent,worked</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sunken</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sunken</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>tiered</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>pit:1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Drops the middle another metre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>gilded</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gilded</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>gilded</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bone_strewn</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Bone-Strewn</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>grim</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>bone_litter</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>blood_stained</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Blood-Stained</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>grim</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>goblin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Goblin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>kobold</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kobold</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>dwarf</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Dwarven</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Orcish</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>martial</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>hobgoblin</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hobgoblin</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>martial</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ratkin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ratkin</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>infested</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>troll</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Troll</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>pilgrim</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pilgrims'</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>7</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>sacred</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>monk</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Monks'</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>7</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>sacred</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>miner</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Miners'</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>9</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>smuggler</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Smugglers'</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>7</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cultist</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cultists'</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>profane</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>bandit</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Bandits'</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>8</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>martial</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>nameless</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nameless</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>people</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6505,6 +9526,146 @@
       <c r="D74" t="inlineStr">
         <is>
           <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>world.room_named_chance</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>world.room_condition_chance</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>world.room_people_chance</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>world.room_shape_ramps</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ways up</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>world.room_shape_min_side</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>metres</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>room.study_difficulty</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>13</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>room.study_ticks</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>45</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ticks</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>How long a crawler spends looking at a room between attempts to read it.</t>
         </is>
       </c>
     </row>
@@ -6628,7 +9789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7148,6 +10309,42 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>following</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ui.doing_studying</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>reading the room</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ui.label_place</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ui.place_unknown</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nobody has read this place yet</t>
         </is>
       </c>
     </row>
@@ -7162,7 +10359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7694,6 +10891,414 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>Carried for luck, or for something worse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>flooded</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>flooded</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Standing water has taken the lower ground here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>frozen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>frozen</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cold enough that the water has not moved in a long time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>burnt</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>burnt</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Fire went through here and left it black.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>collapsed</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>collapsed</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>The ceiling or the walls came down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>abandoned</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>abandoned</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Left in a hurry, or left to rot. Nobody has kept it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>haunted</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>haunted</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Something of what happened here has not finished happening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cursed</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cursed</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Deliberately spoiled, by somebody who knew how.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>overgrown</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>overgrown</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Growing things have taken it back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>infested</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>infested</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Something lives here now, and it is not people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sacred</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sacred</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Built to be knelt in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>profane</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>profane</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Built for something people do not admit to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Shaped by hand: cut, dressed, laid out on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>buried</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>buried</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Half filled in by what fell on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>pillared</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>pillared</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Columns hold the roof up, and break the sightlines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tiered</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tiered</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The floor is on more than one level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>gilded</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gilded</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Somebody spent money here once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Too quiet. Sound does not carry the way it should.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Work was done here, at scale, with tools and heat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dwelling</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>dwelling</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>People slept here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Things were kept here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>learning</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>learning</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Knowledge was kept or made here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>captivity</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>captivity</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>People were held here against their will.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>martial</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>martial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Soldiers used it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>room</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>room</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>A place in the labyrinth large enough to have been something.</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -1906,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="K3" t="n">
         <v>0.05</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>#5c5145</t>
+          <t>#6b5f4f</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1980,19 +1980,19 @@
         <v>-0.26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="K4" t="n">
-        <v>0.155</v>
+        <v>0.185</v>
       </c>
       <c r="L4" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="N4" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.16</v>
       </c>
       <c r="S4" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>#33302c</t>
+          <t>#4a4238</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2079,7 +2079,7 @@
         <v>0.06</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0.1</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>#5c5145</t>
+          <t>#6b5f4f</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2123,22 +2123,22 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="J6" t="n">
         <v>0.03</v>
       </c>
       <c r="K6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.052</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.044</v>
-      </c>
       <c r="M6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.052</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.044</v>
       </c>
       <c r="O6" t="n">
         <v>6</v>
@@ -2153,7 +2153,7 @@
         <v>0.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2194,22 +2194,22 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.24</v>
+        <v>-0.29</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="K7" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.044</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.038</v>
-      </c>
       <c r="M7" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.044</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.038</v>
       </c>
       <c r="O7" t="n">
         <v>6</v>
@@ -2221,10 +2221,10 @@
         <v>0.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>-0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="K8" t="n">
         <v>0.042</v>
@@ -2292,7 +2292,7 @@
         <v>0.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0.3</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>#33302c</t>
+          <t>#554b3e</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2336,22 +2336,22 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="J9" t="n">
         <v>0.04</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="L9" t="n">
         <v>0.058</v>
       </c>
       <c r="M9" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
@@ -2366,7 +2366,7 @@
         <v>0.14</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>#33302c</t>
+          <t>#483f34</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2407,22 +2407,22 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="L10" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
@@ -2434,10 +2434,10 @@
         <v>0.09</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>#2b2825</t>
+          <t>#3a322a</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2478,10 +2478,10 @@
         <v>0.025</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="K11" t="n">
         <v>0.054</v>
@@ -2505,7 +2505,7 @@
         <v>0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0.1</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>#5c5145</t>
+          <t>#6b5f4f</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2549,22 +2549,22 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="J12" t="n">
         <v>0.03</v>
       </c>
       <c r="K12" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.052</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.044</v>
-      </c>
       <c r="M12" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.052</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.044</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -2579,7 +2579,7 @@
         <v>0.1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -2620,22 +2620,22 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.24</v>
+        <v>-0.29</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="K13" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.044</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.038</v>
-      </c>
       <c r="M13" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N13" t="n">
         <v>0.044</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.038</v>
       </c>
       <c r="O13" t="n">
         <v>6</v>
@@ -2647,10 +2647,10 @@
         <v>0.05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         <v>-0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="K14" t="n">
         <v>0.042</v>
@@ -2718,7 +2718,7 @@
         <v>0.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0.3</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>#33302c</t>
+          <t>#554b3e</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2762,22 +2762,22 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="J15" t="n">
         <v>0.04</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="L15" t="n">
         <v>0.058</v>
       </c>
       <c r="M15" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="O15" t="n">
         <v>6</v>
@@ -2792,7 +2792,7 @@
         <v>0.14</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>#33302c</t>
+          <t>#483f34</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2833,22 +2833,22 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="L16" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="N16" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
@@ -2860,10 +2860,10 @@
         <v>0.09</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>#2b2825</t>
+          <t>#3a322a</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2904,10 +2904,10 @@
         <v>0.025</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="K17" t="n">
         <v>0.054</v>
@@ -2931,7 +2931,7 @@
         <v>0.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0.1</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>#3a352f</t>
+          <t>#4c463d</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3054,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K19" t="n">
         <v>0.076</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>#6b5335</t>
+          <t>#7a6041</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3211,19 +3211,19 @@
         <v>-0.27</v>
       </c>
       <c r="J21" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.166</v>
+        <v>0.196</v>
       </c>
       <c r="L21" t="n">
-        <v>0.13</v>
+        <v>0.126</v>
       </c>
       <c r="M21" t="n">
-        <v>0.111</v>
+        <v>0.116</v>
       </c>
       <c r="N21" t="n">
-        <v>0.093</v>
+        <v>0.095</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
@@ -3238,7 +3238,7 @@
         <v>0.14</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3283,22 +3283,22 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L22" t="n">
         <v>0.052</v>
       </c>
-      <c r="L22" t="n">
-        <v>0.046</v>
-      </c>
       <c r="M22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.052</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.046</v>
       </c>
       <c r="O22" t="n">
         <v>6</v>
@@ -3310,10 +3310,10 @@
         <v>0.06</v>
       </c>
       <c r="R22" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>-0.09</v>
       </c>
       <c r="J23" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K23" t="n">
         <v>0.05</v>
@@ -3385,7 +3385,7 @@
         <v>0.05</v>
       </c>
       <c r="R23" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0.28</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>#4a4136</t>
+          <t>#5d5243</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3433,22 +3433,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.43</v>
+        <v>-0.46</v>
       </c>
       <c r="J24" t="n">
         <v>0.06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
       <c r="L24" t="n">
         <v>0.066</v>
       </c>
       <c r="M24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>6</v>
@@ -3463,7 +3463,7 @@
         <v>0.12</v>
       </c>
       <c r="S24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>#3b2f22</t>
+          <t>#4e4032</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3508,22 +3508,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="K25" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="L25" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="M25" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="O25" t="n">
         <v>6</v>
@@ -3535,10 +3535,10 @@
         <v>0.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>#3b2f22</t>
+          <t>#4a3d30</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3583,10 +3583,10 @@
         <v>0.025</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K26" t="n">
         <v>0.062</v>
@@ -3610,7 +3610,7 @@
         <v>0.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0.08</v>
@@ -3658,22 +3658,22 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L27" t="n">
         <v>0.052</v>
       </c>
-      <c r="L27" t="n">
-        <v>0.046</v>
-      </c>
       <c r="M27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N27" t="n">
         <v>0.052</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.046</v>
       </c>
       <c r="O27" t="n">
         <v>6</v>
@@ -3685,10 +3685,10 @@
         <v>0.06</v>
       </c>
       <c r="R27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>-0.09</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K28" t="n">
         <v>0.05</v>
@@ -3760,7 +3760,7 @@
         <v>0.05</v>
       </c>
       <c r="R28" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0.28</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>#4a4136</t>
+          <t>#5d5243</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3808,22 +3808,22 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.43</v>
+        <v>-0.46</v>
       </c>
       <c r="J29" t="n">
         <v>0.06</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
       <c r="L29" t="n">
         <v>0.066</v>
       </c>
       <c r="M29" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>6</v>
@@ -3838,7 +3838,7 @@
         <v>0.12</v>
       </c>
       <c r="S29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>#3b2f22</t>
+          <t>#4e4032</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3883,22 +3883,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="J30" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="K30" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="L30" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="M30" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="O30" t="n">
         <v>6</v>
@@ -3910,10 +3910,10 @@
         <v>0.1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>#3b2f22</t>
+          <t>#4a3d30</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3958,10 +3958,10 @@
         <v>0.025</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K31" t="n">
         <v>0.062</v>
@@ -3985,7 +3985,7 @@
         <v>0.05</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0.08</v>
@@ -12564,7 +12564,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.155</v>
+        <v>0.175</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.155</v>
+        <v>-0.175</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.095</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -8042,7 +8042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9666,6 +9666,146 @@
       <c r="D81" t="inlineStr">
         <is>
           <t>How long a crawler spends looking at a room between attempts to read it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>texture.masonry_px</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>32</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>The size of the repeating masonry tile. At 32 pixels to the metre, 32 means the pattern repeats every square metre of wall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>texture.masonry_mortar</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>texture.masonry_variation</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>texture.masonry_course_min</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>The shortest a course of stones may be, about 9cm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>texture.masonry_course_max</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>texture.masonry_stone_min</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>The narrowest a single stone may be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>texture.masonry_stone_max</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>11</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11299,6 +11439,23 @@
       <c r="C55" t="inlineStr">
         <is>
           <t>A place in the labyrinth large enough to have been something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>constructed</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>constructed</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Built by hand out of separate pieces -- laid, fitted and mortared, rather than cut out of the living rock.</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11321,10 +11478,11 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="78" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11355,20 +11513,25 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>footing</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>cross</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -11400,18 +11563,19 @@
           <t>#585c61</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>7</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>11</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Worked flagstone. The default footing of the labyrinth.</t>
         </is>
@@ -11443,18 +11607,19 @@
           <t>#63553f</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>8</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Trodden soil.</t>
         </is>
@@ -11486,18 +11651,19 @@
           <t>#4a5c45</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>14</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Stone gone green where the water sits.</t>
         </is>
@@ -11529,18 +11695,19 @@
           <t>#335667</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>13</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>18</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Ankle deep. Slows a walker, ruins what it soaks.</t>
         </is>
@@ -11572,18 +11739,19 @@
           <t>#57534c</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>14</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>17</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Collapsed masonry, not yet cleared.</t>
         </is>
@@ -11615,18 +11783,19 @@
           <t>#6f6959</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>9</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>13</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Somebody else got this far.</t>
         </is>
@@ -11658,18 +11827,19 @@
           <t>#5b5f64</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>ramp</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>11</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>15</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>A climbable one-metre slope.</t>
         </is>
@@ -11701,20 +11871,69 @@
           <t>#46494d</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>block</t>
         </is>
-      </c>
-      <c r="G9" t="n">
-        <v>99</v>
       </c>
       <c r="H9" t="n">
         <v>99</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>99</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>A full cubic metre of rock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>stone_wall</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Stone Block Wall</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>stone,constructed,solid,blocks-sight</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>#b9b2a1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>#a79e8c</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>masonry</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>99</v>
+      </c>
+      <c r="I10" t="n">
+        <v>99</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Rough limestone blocks laid and fitted by somebody's hands, big ones and small ones packed together. Somebody built this.</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -22,6 +22,7 @@
     <sheet name="figure" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="structures" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="words" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="structure_parts" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8036,13 +8037,1619 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="78" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>spin</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>from_m</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>to_m</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>w_top</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>w_bot</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>d_top</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>d_bot</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>sides</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>rings</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>bulge</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>cap_top</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>cap_bot</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>glow</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>grows</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fire_stone_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hearth Stone</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>#6e6960</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>One of the ring of stones somebody dragged round the fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fire_stone_1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hearth Stone</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>#6e6960</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>One of the ring of stones somebody dragged round the fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fire_stone_2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hearth Stone</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>#6e6960</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.267</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>One of the ring of stones somebody dragged round the fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fire_log_0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Log</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>#4a3a26</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leaning into the middle, the way you actually build a fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fire_log_1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Log</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>#4a3a26</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>58</v>
+      </c>
+      <c r="I6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leaning into the middle, the way you actually build a fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fire_log_2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Log</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>#4a3a26</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.173</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>58</v>
+      </c>
+      <c r="I7" t="n">
+        <v>240</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leaning into the middle, the way you actually build a fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fire_flame</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flame</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>#e8923a</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Only burns once the fire is finished. glow 1: it IS the light.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fire_ember</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Embers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>campfire</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>#c2521c</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bed_mat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bedroll</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>#6b5a44</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lies down: lean 90 turns the lathe on its side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bed_roll</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Blanket Roll</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bedroll</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>#7d6a4e</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>90</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rolled at the head end. Only there once it is made up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>store_barrel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Barrel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>#5d4a30</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>The bulge is what makes a lathe a barrel rather than a drum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>store_hoop_0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hoop</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>#3b3229</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>An iron band round the staves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>store_hoop_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hoop</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>#3b3229</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>An iron band round the staves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>store_lid</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lid</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>#6b5738</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Goes on last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>wind_post_0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>windbreak</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>#4f4436</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>270</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Driven into the floor and leaning back a little.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>wind_post_1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>windbreak</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>#4f4436</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>90</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Driven into the floor and leaning back a little.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wind_rail</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cross-piece</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>windbreak</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>#4f4436</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H18" t="n">
+        <v>90</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wind_cloth</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cloth</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>windbreak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>#6a5f4b</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stretched between the posts once they are standing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9672,31 +11279,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>texture.masonry_px</t>
+          <t>texture.masonry_mortar</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32</v>
+        <v>0.38</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>The size of the repeating masonry tile. At 32 pixels to the metre, 32 means the pattern repeats every square metre of wall.</t>
+          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>texture.masonry_mortar</t>
+          <t>texture.masonry_variation</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9705,38 +11312,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
+          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>texture.masonry_variation</t>
+          <t>texture.masonry_course_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>pixels</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+          <t>The shortest a course of stones may be, about 9cm.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>texture.masonry_course_min</t>
+          <t>texture.masonry_course_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9745,18 +11352,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The shortest a course of stones may be, about 9cm.</t>
+          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>texture.masonry_course_max</t>
+          <t>texture.masonry_stone_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9765,18 +11372,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+          <t>The narrowest a single stone may be.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_min</t>
+          <t>texture.masonry_stone_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9785,18 +11392,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>The narrowest a single stone may be.</t>
+          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_max</t>
+          <t>texture.pattern_px</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9805,7 +11412,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
+          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>texture.hue_shift</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
         </is>
       </c>
     </row>
@@ -11555,15 +13182,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>#6e7278</t>
+          <t>#6f6a63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#585c61</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>#544f49</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>flagstone</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>walk</t>
@@ -11599,15 +13230,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>#7d6c54</t>
+          <t>#6b5a45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>#63553f</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>#51422f</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dirt</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>walk</t>
@@ -11643,15 +13278,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>#5f7557</t>
+          <t>#5c6a52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>#4a5c45</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>#42503c</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>moss</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>walk</t>
@@ -11687,15 +13326,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>#3f6b7d</t>
+          <t>#40606b</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>#335667</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>#2e4a55</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>walk</t>
@@ -11731,15 +13374,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>#6d6860</t>
+          <t>#6a655c</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>#57534c</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>#4e4a43</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rubble</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>walk</t>
@@ -11775,15 +13422,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>#8d8672</t>
+          <t>#837b68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>#6f6959</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>#635c4e</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>bones</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>walk</t>
@@ -11819,15 +13470,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>#73777d</t>
+          <t>#747069</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>#5b5f64</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>#57534d</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>flagstone</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>ramp</t>
@@ -11863,15 +13518,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>#5a5d62</t>
+          <t>#5c5954</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>#46494d</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>#45423e</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>block</t>
@@ -11907,12 +13566,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>#b9b2a1</t>
+          <t>#8d8676</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>#a79e8c</t>
+          <t>#6f6a5d</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -9649,7 +9649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10863,143 +10863,143 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>texture.floor_px</t>
+          <t>texture.strength</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How big one square of the ground's grain is. The grain repeats every this many pixels across the floor.</t>
+          <t>How strongly a material marks the surface it is on. 0 leaves every tile a plain flat colour.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>texture.fine_px</t>
+          <t>texture.seed</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>How big the grain is on crawlers and on anything built. Smaller than the floor's, because a face is only about eight pixels across.</t>
+          <t>Which set of materials gets generated. Change it for a different cut of stone, spread of moss and scatter of rubble.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>texture.strength</t>
+          <t>render.min_face_px</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>How strongly the grain darkens and lightens what is underneath. 0 turns texture off entirely.</t>
+          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>texture.speck</t>
+          <t>roll.dice</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.055</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>How much of the grain is hard specks of grit and rust rather than soft mottling.</t>
+          <t>How many dice are thrown for an attempt. Two gives a bell: middling results are common, extremes are rare.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>texture.seed</t>
+          <t>roll.die_faces</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7</v>
-      </c>
-      <c r="C65" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>faces</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Which grain gets generated. Change it for a different pattern of grit.</t>
+          <t>How many faces each die has.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>render.min_face_px</t>
+          <t>light.ambient</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
+          <t>How much you can see where nothing is lighting the way. Very low: the labyrinth is dark, and light is something you carry into it.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>roll.dice</t>
+          <t>light.warmth</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>How many dice are thrown for an attempt. Two gives a bell: middling results are common, extremes are rare.</t>
+          <t>How much a lit thing goes orange rather than just brighter. 0 is cold light, 1 is firelight.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>roll.die_faces</t>
+          <t>light.steps</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -11007,323 +11007,323 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>faces</t>
+          <t>steps</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>How many faces each die has.</t>
+          <t>How many levels of brightness there are between dark and fully lit. Few levels look painted; many look smooth and cost more to draw.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>light.ambient</t>
+          <t>light.falloff</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.14</v>
+        <v>1.35</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>How much you can see where nothing is lighting the way. Very low: the labyrinth is dark, and light is something you carry into it.</t>
+          <t>How sharply light dies with distance. Above 1 keeps the bright part close to the source.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>light.warmth</t>
+          <t>anim.step_ticks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.45</v>
+        <v>22</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>How much a lit thing goes orange rather than just brighter. 0 is cold light, 1 is firelight.</t>
+          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>light.steps</t>
+          <t>camera.follow</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>steps</t>
+          <t>0 or 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>How many levels of brightness there are between dark and fully lit. Few levels look painted; many look smooth and cost more to draw.</t>
+          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>light.falloff</t>
+          <t>world.room_named_chance</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.35</v>
+        <v>0.5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>How sharply light dies with distance. Above 1 keeps the bright part close to the source.</t>
+          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>anim.step_ticks</t>
+          <t>world.room_condition_chance</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>22</v>
+        <v>0.55</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
+          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>camera.follow</t>
+          <t>world.room_people_chance</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0 or 1</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
+          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>world.room_named_chance</t>
+          <t>world.room_shape_ramps</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>ways up</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
+          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>world.room_condition_chance</t>
+          <t>world.room_shape_min_side</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.55</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
+          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>world.room_people_chance</t>
+          <t>room.study_difficulty</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.45</v>
+        <v>13</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
+          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>world.room_shape_ramps</t>
+          <t>room.study_ticks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ways up</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
+          <t>How long a crawler spends looking at a room between attempts to read it.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>world.room_shape_min_side</t>
+          <t>texture.masonry_mortar</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>0.38</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
+          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>room.study_difficulty</t>
+          <t>texture.masonry_variation</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13</v>
+        <v>0.3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
+          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>room.study_ticks</t>
+          <t>texture.masonry_course_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>pixels</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>How long a crawler spends looking at a room between attempts to read it.</t>
+          <t>The shortest a course of stones may be, about 9cm.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>texture.masonry_mortar</t>
+          <t>texture.masonry_course_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.38</v>
+        <v>7</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>pixels</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
+          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>texture.masonry_variation</t>
+          <t>texture.masonry_stone_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>pixels</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+          <t>The narrowest a single stone may be.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>texture.masonry_course_min</t>
+          <t>texture.masonry_stone_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11332,18 +11332,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The shortest a course of stones may be, about 9cm.</t>
+          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>texture.masonry_course_max</t>
+          <t>texture.pattern_px</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11352,85 +11352,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_min</t>
+          <t>texture.hue_shift</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>0.28</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
-        <is>
-          <t>The narrowest a single stone may be.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>texture.masonry_stone_max</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>11</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>pixels</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>texture.pattern_px</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>32</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>pixels</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>texture.hue_shift</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0 to 1</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
         <is>
           <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
         </is>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -1176,7 +1176,6 @@
           <t>willpower:1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -1212,7 +1211,6 @@
           <t>presence:1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0</v>
       </c>
@@ -1288,7 +1286,6 @@
           <t>endurance:1,agility:-1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
@@ -1319,7 +1316,6 @@
           <t>leather</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>labouring:2,tinkering:1</t>
@@ -1355,7 +1351,6 @@
           <t>iron,wood,tool</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>labouring:3,building:3</t>
@@ -1391,7 +1386,6 @@
           <t>iron,glass,light</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>studying:2,foraging:1</t>
@@ -1427,7 +1421,6 @@
           <t>leather,tool</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>crafting:2,building:1</t>
@@ -1468,7 +1461,6 @@
           <t>endurance:1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>0</v>
       </c>
@@ -1499,7 +1491,6 @@
           <t>leather</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>clambering:2,ranging:2</t>
@@ -1535,7 +1526,6 @@
           <t>rope</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>clambering:1</t>
@@ -1576,7 +1566,6 @@
           <t>willpower:1,presence:-1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>0</v>
       </c>
@@ -1607,8 +1596,6 @@
           <t>wood,fire,light</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>8</v>
       </c>
@@ -1639,7 +1626,6 @@
           <t>fire,light</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>studying:1</t>
@@ -1814,7 +1800,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>head</t>
@@ -1889,7 +1874,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>neck</t>
@@ -1942,7 +1926,6 @@
       <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1960,7 +1943,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>chest</t>
@@ -2035,7 +2017,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>hips</t>
@@ -2088,7 +2069,6 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2106,7 +2086,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>shoulder_l</t>
@@ -2159,7 +2138,6 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2177,7 +2155,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>elbow_l</t>
@@ -2230,7 +2207,6 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2248,7 +2224,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>hand_l</t>
@@ -2301,7 +2276,6 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2319,7 +2293,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>thigh_l</t>
@@ -2372,7 +2345,6 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2390,7 +2362,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>knee_l</t>
@@ -2443,7 +2414,6 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2461,7 +2431,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>foot_l</t>
@@ -2514,7 +2483,6 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2532,7 +2500,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>shoulder_r</t>
@@ -2585,7 +2552,6 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2603,7 +2569,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>elbow_r</t>
@@ -2656,7 +2621,6 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2674,7 +2638,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>hand_r</t>
@@ -2727,7 +2690,6 @@
       <c r="T14" t="n">
         <v>0</v>
       </c>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2745,7 +2707,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>thigh_r</t>
@@ -2798,7 +2759,6 @@
       <c r="T15" t="n">
         <v>0</v>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2816,7 +2776,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>knee_r</t>
@@ -2869,7 +2828,6 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2887,7 +2845,6 @@
           <t>body</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>foot_r</t>
@@ -2940,7 +2897,6 @@
       <c r="T17" t="n">
         <v>0</v>
       </c>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3015,7 +2971,6 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3090,7 +3045,6 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3244,7 +3198,6 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3319,7 +3272,6 @@
       <c r="T22" t="n">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3394,7 +3346,6 @@
       <c r="T23" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3469,7 +3420,6 @@
       <c r="T24" t="n">
         <v>0</v>
       </c>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3544,7 +3494,6 @@
       <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3619,7 +3568,6 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3694,7 +3642,6 @@
       <c r="T27" t="n">
         <v>0</v>
       </c>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3769,7 +3716,6 @@
       <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3844,7 +3790,6 @@
       <c r="T29" t="n">
         <v>0</v>
       </c>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3919,7 +3864,6 @@
       <c r="T30" t="n">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3994,7 +3938,6 @@
       <c r="T31" t="n">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4069,7 +4012,6 @@
       <c r="T32" t="n">
         <v>0</v>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4144,7 +4086,6 @@
       <c r="T33" t="n">
         <v>0</v>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4219,7 +4160,6 @@
       <c r="T34" t="n">
         <v>0</v>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4294,7 +4234,6 @@
       <c r="T35" t="n">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4527,7 +4466,6 @@
       <c r="T38" t="n">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4681,7 +4619,6 @@
       <c r="T40" t="n">
         <v>0</v>
       </c>
-      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4756,7 +4693,6 @@
       <c r="T41" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5118,7 +5054,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>A raised altar end and a short colonnade.</t>
@@ -5159,7 +5094,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>A sunken nave, columns down both sides, a raised apse. Wants a big room.</t>
@@ -5200,7 +5134,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>One raised step with something on it.</t>
@@ -5291,7 +5224,6 @@
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5372,7 +5304,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>A deep tank. Usually wet.</t>
@@ -5418,7 +5349,6 @@
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5454,8 +5384,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5496,7 +5424,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5532,8 +5459,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5569,8 +5494,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5606,8 +5529,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5688,8 +5609,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5725,8 +5644,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5767,7 +5684,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5803,8 +5719,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5840,8 +5754,6 @@
           <t>packed_earth</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5877,8 +5789,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5914,8 +5824,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5956,7 +5864,6 @@
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5997,7 +5904,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6038,7 +5944,6 @@
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6074,8 +5979,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6111,8 +6014,6 @@
           <t>packed_earth</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6148,8 +6049,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6185,8 +6084,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6222,8 +6119,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6264,7 +6159,6 @@
           <t>rubble</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6305,7 +6199,6 @@
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6346,7 +6239,6 @@
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6382,8 +6274,6 @@
           <t>packed_earth</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6419,8 +6309,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6456,8 +6344,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6498,7 +6384,6 @@
           <t>packed_earth</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6539,7 +6424,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6575,8 +6459,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6617,7 +6499,6 @@
           <t>packed_earth</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6653,8 +6534,6 @@
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6690,7 +6569,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Wants a big room. Everything points at one raised seat.</t>
@@ -6731,8 +6609,6 @@
           <t>stone_floor</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6763,8 +6639,6 @@
           <t>water:1</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Fills the lowest ground with standing water.</t>
@@ -6800,13 +6674,11 @@
           <t>water:2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6832,10 +6704,6 @@
           <t>frozen,dry</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6866,9 +6734,6 @@
           <t>rubble:1</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6894,10 +6759,6 @@
           <t>burnt,dry</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6933,8 +6794,6 @@
           <t>rubble</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6965,13 +6824,11 @@
           <t>rubble:2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>rubble</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7002,9 +6859,6 @@
           <t>rubble:2,terrace:2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7035,9 +6889,6 @@
           <t>rubble:2,platform:1</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7063,10 +6914,6 @@
           <t>abandoned</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7092,10 +6939,6 @@
           <t>abandoned,silent</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7121,10 +6964,6 @@
           <t>abandoned,grim</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7150,10 +6989,6 @@
           <t>haunted,grim</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7184,13 +7019,11 @@
           <t>water:1</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7216,10 +7049,6 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7245,14 +7074,11 @@
           <t>cursed,grim</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7283,13 +7109,11 @@
           <t>rubble:1</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7315,14 +7139,11 @@
           <t>overgrown,organic,damp</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7348,14 +7169,11 @@
           <t>overgrown,damp</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>moss_stone</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7381,7 +7199,6 @@
           <t>overgrown,organic,damp</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>moss_stone</t>
@@ -7392,7 +7209,6 @@
           <t>shallow_water</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7418,10 +7234,6 @@
           <t>infested</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7452,9 +7264,6 @@
           <t>rubble:1</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7480,10 +7289,6 @@
           <t>silent,worked</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7514,8 +7319,6 @@
           <t>pit:1</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Drops the middle another metre.</t>
@@ -7546,10 +7349,6 @@
           <t>gilded</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7575,14 +7374,11 @@
           <t>grim</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>bone_litter</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7608,10 +7404,6 @@
           <t>grim</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7632,11 +7424,6 @@
       <c r="D71" t="n">
         <v>12</v>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7657,11 +7444,6 @@
       <c r="D72" t="n">
         <v>10</v>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7687,10 +7469,6 @@
           <t>worked</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7716,10 +7494,6 @@
           <t>martial</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7745,10 +7519,6 @@
           <t>martial</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7774,10 +7544,6 @@
           <t>infested</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7798,11 +7564,6 @@
       <c r="D77" t="n">
         <v>5</v>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7823,11 +7584,6 @@
       <c r="D78" t="n">
         <v>10</v>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7853,10 +7609,6 @@
           <t>sacred</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7882,10 +7634,6 @@
           <t>sacred</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7911,10 +7659,6 @@
           <t>industry</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7940,10 +7684,6 @@
           <t>storage</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7969,10 +7709,6 @@
           <t>profane</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7998,10 +7734,6 @@
           <t>martial</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8027,10 +7759,6 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8830,7 +8558,6 @@
       <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9555,7 +9282,6 @@
       <c r="V18" t="n">
         <v>1</v>
       </c>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9649,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10889,7 +10615,6 @@
       <c r="B62" t="n">
         <v>7</v>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Which set of materials gets generated. Change it for a different cut of stone, spread of moss and scatter of rubble.</t>
@@ -11179,151 +10904,151 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>room.study_difficulty</t>
+          <t>world.join_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>doorways</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
+          <t>The fewest ways out of a piece into the piece next door. One is the smallest number that keeps the promise that you can always walk onward, so this dial must never be set below 1.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>room.study_ticks</t>
+          <t>world.join_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>doorways</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>How long a crawler spends looking at a room between attempts to read it.</t>
+          <t>The most ways out of a piece into the piece next door. Every doorway is dug from the edge of the piece to one of its rooms, so more doorways means more corridors, more ways round, and fewer rooms left sealed off.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>texture.masonry_mortar</t>
+          <t>world.join_margin</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.38</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>tiles</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
+          <t>How far a doorway keeps from the corner of a piece. Doorways from all four neighbouring pieces crowd into a corner, so this is what stops the four corners of the world meeting in one heap.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>texture.masonry_variation</t>
+          <t>room.study_difficulty</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.3</v>
+        <v>13</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>texture.masonry_course_min</t>
+          <t>room.study_ticks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The shortest a course of stones may be, about 9cm.</t>
+          <t>How long a crawler spends looking at a room between attempts to read it.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>texture.masonry_course_max</t>
+          <t>texture.masonry_mortar</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>0.38</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_min</t>
+          <t>texture.masonry_variation</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>The narrowest a single stone may be.</t>
+          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_max</t>
+          <t>texture.masonry_course_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11332,18 +11057,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
+          <t>The shortest a course of stones may be, about 9cm.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>texture.pattern_px</t>
+          <t>texture.masonry_course_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11352,25 +11077,85 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
+          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>texture.masonry_stone_min</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>The narrowest a single stone may be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>texture.masonry_stone_max</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>11</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>texture.pattern_px</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>32</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>texture.hue_shift</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B89" t="n">
         <v>0.28</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>0 to 1</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
         </is>
@@ -13780,7 +13565,6 @@
           <t>might:1,agility:1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>0</v>
       </c>
@@ -13836,7 +13620,6 @@
           <t>might:1,presence:1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0</v>
       </c>
@@ -13892,7 +13675,6 @@
           <t>might:1,willpower:1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>0</v>
       </c>
@@ -13918,7 +13700,6 @@
           <t>agility:1,endurance:1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>0</v>
       </c>
@@ -13944,7 +13725,6 @@
           <t>agility:1,presence:1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>0</v>
       </c>
@@ -14030,7 +13810,6 @@
           <t>endurance:1,presence:1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>0</v>
       </c>
@@ -14056,7 +13835,6 @@
           <t>endurance:1,intellect:1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>0</v>
       </c>
@@ -14082,7 +13860,6 @@
           <t>endurance:1,willpower:1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>0</v>
       </c>
@@ -14108,7 +13885,6 @@
           <t>presence:1,intellect:1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>0</v>
       </c>
@@ -14134,7 +13910,6 @@
           <t>presence:1,willpower:1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>0</v>
       </c>
@@ -14160,7 +13935,6 @@
           <t>intellect:1,willpower:1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>0</v>
       </c>
@@ -14241,7 +14015,6 @@
           <t>Root</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>0</v>
       </c>
@@ -14282,7 +14055,6 @@
       <c r="F3" t="n">
         <v>0.82</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14309,7 +14081,6 @@
       <c r="F4" t="n">
         <v>0.26</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14336,7 +14107,6 @@
       <c r="F5" t="n">
         <v>0.24</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14363,7 +14133,6 @@
       <c r="F6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14390,7 +14159,6 @@
       <c r="F7" t="n">
         <v>0.17</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14417,7 +14185,6 @@
       <c r="F8" t="n">
         <v>0.17</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14444,7 +14211,6 @@
       <c r="F9" t="n">
         <v>-0.26</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14471,7 +14237,6 @@
       <c r="F10" t="n">
         <v>-0.26</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14560,7 +14325,6 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14587,7 +14351,6 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14614,7 +14377,6 @@
       <c r="F15" t="n">
         <v>-0.42</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14641,7 +14403,6 @@
       <c r="F16" t="n">
         <v>-0.42</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14668,7 +14429,6 @@
       <c r="F17" t="n">
         <v>-0.38</v>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14695,7 +14455,6 @@
       <c r="F18" t="n">
         <v>-0.38</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -9375,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11158,6 +11158,46 @@
       <c r="D89" t="inlineStr">
         <is>
           <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>world.chunks_per_frame</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>pieces</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>How many new pieces of labyrinth the game may cut in one frame of the picture (60 frames a second). A piece is real work to make, so they arrive a few at a time rather than all at once, and the picture stays smooth. Raise it to lay ground down faster; lower it if walking into new ground ever stutters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>world.live_ring</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>pieces</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>How many pieces of ground are kept ready BEYOND what you can see, and beyond every crawler and every camp site. This ring is what stops a crawler reaching ground that has not been made yet. Every piece kept is a piece's worth of rooms held in memory and walked over by the picture, so a bigger ring is heavier: raise it only if new ground ever appears too late.</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -9375,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9449,31 +9449,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>render.occluder_fade</t>
+          <t>render.side_shade_left</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.28</v>
+        <v>0.78</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>How solid a block stays when it is standing between you and the tile you are inspecting. 1 = never fades, 0 = disappears entirely.</t>
+          <t>Brightness of the left-facing wall of a block. Below 1 makes it darker than the top.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>render.side_shade_left</t>
+          <t>render.side_shade_right</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -9482,114 +9482,114 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brightness of the left-facing wall of a block. Below 1 makes it darker than the top.</t>
+          <t>Brightness of the right-facing wall of a block.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>render.side_shade_right</t>
+          <t>render.height_tint</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x/m</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brightness of the right-facing wall of a block.</t>
+          <t>How much lighter a surface gets per metre of elevation. Gives depth without lighting.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>render.height_tint</t>
+          <t>camera.key_pan_speed</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.035</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x/m</t>
+          <t>px/tick</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>How much lighter a surface gets per metre of elevation. Gives depth without lighting.</t>
+          <t>How fast the arrow keys slide the view.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>camera.key_pan_speed</t>
+          <t>world.chunk_tiles</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>px/tick</t>
+          <t>tiles</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>How fast the arrow keys slide the view.</t>
+          <t>Width and depth of the piece of labyrinth generated. 56 tiles = 56 metres across.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>world.chunk_tiles</t>
+          <t>world.max_elevation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tiles</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Width and depth of the piece of labyrinth generated. 56 tiles = 56 metres across.</t>
+          <t>How many different floor levels the rooms and halls are spread across.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>world.max_elevation</t>
+          <t>roll.attribute_weight</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>How many different floor levels the rooms and halls are spread across.</t>
+          <t>How much a natural attribute is worth in a roll. At 1, an attribute of 4 is worth 4 -- the number on the sheet is the number in the roll.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>roll.attribute_weight</t>
+          <t>roll.skill_weight</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -9602,38 +9602,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>How much a natural attribute is worth in a roll. At 1, an attribute of 4 is worth 4 -- the number on the sheet is the number in the roll.</t>
+          <t>How much practice is worth in a roll. At 1, a skill of 3 is worth 3.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>roll.skill_weight</t>
+          <t>skill.cap</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>How much practice is worth in a roll. At 1, a skill of 3 is worth 3.</t>
+          <t>The most practice any one skill can hold. Six, the same scale as an attribute.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skill.cap</t>
+          <t>learn.gain_on_failure</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>0.1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -9642,18 +9642,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The most practice any one skill can hold. Six, the same scale as an attribute.</t>
+          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a crawler learns. Ten failures is a tenth of the way to mastery.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>learn.gain_on_failure</t>
+          <t>learn.gain_on_success</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -9662,18 +9662,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Practice gained from a FAILED attempt. Rule 1: failing is how a crawler learns. Ten failures is a tenth of the way to mastery.</t>
+          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>learn.gain_on_success</t>
+          <t>learn.near_miss_bonus</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -9682,18 +9682,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Practice gained from a successful attempt. Zero: succeeding teaches nothing at all, so a crawler who has mastered something stops improving until the labyrinth gives them something harder.</t>
+          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>learn.near_miss_bonus</t>
+          <t>learn.near_miss_margin</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9702,58 +9702,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Extra practice for only just failing. Getting close teaches most of all.</t>
+          <t>How close a failure has to be to count as only just missing. Two, on a scale where a whole roll is about a dozen.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>learn.near_miss_margin</t>
+          <t>actor.count</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>people</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>How close a failure has to be to count as only just missing. Two, on a scale where a whole roll is about a dozen.</t>
+          <t>How many crawlers turn up in the labyrinth.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>actor.count</t>
+          <t>actor.attribute_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>How many crawlers turn up in the labyrinth.</t>
+          <t>Lowest a natural attribute can be. One to six, like a die: 3 and 4 are ordinary, 1 and 6 are remarkable.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>actor.attribute_min</t>
+          <t>actor.attribute_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -9762,78 +9762,78 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lowest a natural attribute can be. One to six, like a die: 3 and 4 are ordinary, 1 and 6 are remarkable.</t>
+          <t>Highest a natural attribute can be.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>actor.attribute_max</t>
+          <t>actor.step_ticks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Highest a natural attribute can be.</t>
+          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>actor.step_ticks</t>
+          <t>actor.height_m</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>1.625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>How long a crawler pauses between attempts to move. 60 ticks is a second.</t>
+          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>actor.height_m</t>
+          <t>render.zoom_start</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>How tall a grown crawler is. At the locked scale of 32 pixels per metre this makes them 52 pixels tall.</t>
+          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>render.zoom_start</t>
+          <t>render.zoom_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -9842,18 +9842,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>How many real screen pixels one game pixel takes up when the game opens. Zooming does NOT make the world bigger -- it makes the pixels bigger, so the picture stays perfectly sharp.</t>
+          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>render.zoom_min</t>
+          <t>render.zoom_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -9862,38 +9862,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Furthest out. One game pixel to one screen pixel, showing the most ground.</t>
+          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>render.zoom_max</t>
+          <t>render.max_buffer_w</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>960</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Closest in. Whole numbers only, which is what keeps every edge hard.</t>
+          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>render.max_buffer_w</t>
+          <t>render.max_buffer_h</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>960</v>
+        <v>540</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -9902,58 +9902,58 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Widest the game picture is ever drawn, before it is blown up. Caps the work on a very large screen.</t>
+          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>render.max_buffer_h</t>
+          <t>world.rooms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>540</v>
+        <v>9</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tallest the game picture is ever drawn, before it is blown up.</t>
+          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>world.rooms</t>
+          <t>world.room_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rooms</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>How many rooms to carve out of the rock. Halls are then dug between them.</t>
+          <t>Smallest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>world.room_min</t>
+          <t>world.room_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9962,18 +9962,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Smallest a room can be, along one side.</t>
+          <t>Largest a room can be, along one side.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>world.room_max</t>
+          <t>world.hall_width</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9982,14 +9982,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Largest a room can be, along one side.</t>
+          <t>How wide the halls between rooms are.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>world.hall_width</t>
+          <t>world.rock_height</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -10002,174 +10002,174 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>How wide the halls between rooms are.</t>
+          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>world.rock_height</t>
+          <t>camp.bedrolls</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How far the solid rock rises above the floor beside it. This is what makes a wall a wall. Tall rock hides more of what is behind it, so this and the cutaway settings work against each other.</t>
+          <t>How many bedrolls the crawlers lay out around the fire.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>camp.bedrolls</t>
+          <t>camp.stores</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>stores</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How many bedrolls the crawlers lay out around the fire.</t>
+          <t>How many stores the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>camp.stores</t>
+          <t>camp.windbreaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>stores</t>
+          <t>windbreaks</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How many stores the crawlers put up.</t>
+          <t>How many windbreaks the crawlers put up.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>camp.windbreaks</t>
+          <t>camp.site_spread</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>windbreaks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How many windbreaks the crawlers put up.</t>
+          <t>How far from the fire the rest of the camp is laid out.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>camp.site_spread</t>
+          <t>camp.progress_per_success</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pts</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How far from the fire the rest of the camp is laid out.</t>
+          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>camp.progress_per_success</t>
+          <t>camp.work_ticks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pts</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How much of a structure one successful effort raises. 100 finishes it.</t>
+          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>camp.work_ticks</t>
+          <t>render.cut_solid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How long a crawler takes between efforts. 60 ticks is a second.</t>
+          <t>How solid the rock standing in front of a room stays. 0 means it is not painted at all and the room is seen straight through the gap; 1 means it is drawn like any other rock. Anything in between is the haze the game used to have.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>render.cutaway_fade</t>
+          <t>render.cutaway_depth</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How solid a wall of rock stays when it is standing between you and a floor behind it. This is the see-through fourth wall. 1 = never fades and rooms hide behind their own near walls; 0 = those walls vanish entirely.</t>
+          <t>How close rock has to be to the floor it is hiding before it stands in the way. Small numbers cut away only the near wall of a room, which is what you want; large numbers cut away half the labyrinth at once.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>render.cutaway_depth</t>
+          <t>render.wall_fade_m</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -10182,38 +10182,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How close a wall has to be to the floor it is hiding before it turns translucent. Small numbers fade only the near wall of a room, which is what you want; large numbers fade half the labyrinth into a haze.</t>
+          <t>How far down from its top edge a wall fades away to nothing. The top of every wall fades into whatever the picture put behind it, which is what turns the edge where a wall's lid used to be into a soft step. 0 paints walls solid to the top; large numbers erase them.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>render.tile_h_low</t>
+          <t>render.cut_stump_m</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
+          <t>How much of a block that is hidden behind the wall in front stays standing, once `cut_solid` has taken the rest of it away. 0 deletes the whole square, and the floors behind a hidden column begin half a step short of its foot, so the gap shows a strip of nothing at the bottom of the column -- measured at 13,119 pixels of hole over 16 views before this. A metre is a foot of rock you can see a room over and covers it by construction: at 32 pixels to the metre a crawler is 52 pixels tall, so this is a kerb, not a wall.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>render.tile_h_high</t>
+          <t>render.tile_h_low</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -10222,38 +10222,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
+          <t>How tall a square metre of ground looks at the normal angle. Half of tile_w is the classic two-to-one isometric view.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>camera.swing_ms</t>
+          <t>render.tile_h_high</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>320</v>
+        <v>54</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
+          <t>How tall a square metre of ground looks from the raised angle. Bigger means you are looking down more steeply and can see further into rooms. Walls stay the same height either way, so the locked 32 pixels to the metre holds at both angles.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>camera.tilt_ms</t>
+          <t>camera.swing_ms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -10262,58 +10262,58 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>How long the view takes to rise to the higher angle and back.</t>
+          <t>How long the view takes to swing a quarter turn. This runs on real time, not game time, so the swing is smooth whether or not the world is running.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>anim.walk_ticks</t>
+          <t>camera.tilt_ms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34</v>
+        <v>260</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
+          <t>How long the view takes to rise to the higher angle and back.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>anim.walk_leg_swing</t>
+          <t>anim.walk_ticks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>How far the legs swing forward and back while walking.</t>
+          <t>How long one full stride takes. 60 ticks is a second, so smaller is a faster walk.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>anim.walk_knee_bend</t>
+          <t>anim.walk_leg_swing</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -10322,18 +10322,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>How much the trailing knee folds as the leg comes through.</t>
+          <t>How far the legs swing forward and back while walking.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>anim.walk_arm_swing</t>
+          <t>anim.walk_knee_bend</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -10342,78 +10342,78 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>How far the arms swing, opposite to the legs.</t>
+          <t>How much the trailing knee folds as the leg comes through.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>anim.walk_bob</t>
+          <t>anim.walk_arm_swing</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.035</v>
+        <v>26</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>How far a crawler rises and falls with each step.</t>
+          <t>How far the arms swing, opposite to the legs.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>anim.work_ticks</t>
+          <t>anim.walk_bob</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>40</v>
+        <v>0.035</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>How long one swing of a tool takes.</t>
+          <t>How far a crawler rises and falls with each step.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>anim.work_arm_lift</t>
+          <t>anim.work_ticks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>How far the arms come up for a swing of work.</t>
+          <t>How long one swing of a tool takes.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>anim.work_lean</t>
+          <t>anim.work_arm_lift</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -10422,98 +10422,98 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How far a crawler leans into their work.</t>
+          <t>How far the arms come up for a swing of work.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>anim.idle_ticks</t>
+          <t>anim.work_lean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How long one slow breath takes while standing about.</t>
+          <t>How far a crawler leans into their work.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>anim.idle_sway</t>
+          <t>anim.idle_ticks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.5</v>
+        <v>150</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How much a crawler sways while standing about.</t>
+          <t>How long one slow breath takes while standing about.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>anim.turn_ticks</t>
+          <t>anim.idle_sway</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How long a crawler takes to turn to face a new direction.</t>
+          <t>How much a crawler sways while standing about.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>render.light_ambient</t>
+          <t>anim.turn_ticks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.55</v>
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How lit the darkest FACE of something is, once the lamp has reached it. This is the shape of a thing, not how dark the room is -- that is light.ambient.</t>
+          <t>How long a crawler takes to turn to face a new direction.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>render.light_diffuse</t>
+          <t>render.light_ambient</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -10522,193 +10522,193 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How much brighter a face gets for facing the light.</t>
+          <t>How lit the darkest FACE of something is, once the lamp has reached it. This is the shape of a thing, not how dark the room is -- that is light.ambient.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>actor.gear_chance</t>
+          <t>render.light_diffuse</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
+          <t>How much brighter a face gets for facing the light.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>time.max_steps_per_frame</t>
+          <t>actor.gear_chance</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64</v>
+        <v>0.55</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>The most the world is allowed to advance in a single drawn frame. Stops a slow machine, or a tab left in the background, from lurching forward all at once.</t>
+          <t>How likely a crawler is to turn up already wearing any given piece of gear.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>render.outline_width</t>
+          <t>time.max_steps_per_frame</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>How thick the highlight ring around a selected thing is drawn. It is drawn UNDER the thing and half of it is covered, so 2 here shows as a 1 pixel line around the silhouette.</t>
+          <t>The most the world is allowed to advance in a single drawn frame. Stops a slow machine, or a tab left in the background, from lurching forward all at once.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>texture.strength</t>
+          <t>render.outline_width</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How strongly a material marks the surface it is on. 0 leaves every tile a plain flat colour.</t>
+          <t>How thick the highlight ring around a selected thing is drawn. It is drawn UNDER the thing and half of it is covered, so 2 here shows as a 1 pixel line around the silhouette.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>texture.seed</t>
+          <t>texture.strength</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Which set of materials gets generated. Change it for a different cut of stone, spread of moss and scatter of rubble.</t>
+          <t>How strongly a material marks the surface it is on. 0 leaves every tile a plain flat colour.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>render.min_face_px</t>
+          <t>texture.seed</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
+          <t>Which set of materials gets generated. Change it for a different cut of stone, spread of moss and scatter of rubble.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>roll.dice</t>
+          <t>render.min_face_px</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>0.28</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dice</t>
+          <t>px</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>How many dice are thrown for an attempt. Two gives a bell: middling results are common, extremes are rare.</t>
+          <t>Faces smaller than this many pixels are not drawn. At 32 pixels to the metre a crawler has a lot of surfaces that never cover a whole pixel, and skipping them costs nothing to look at and saves a great deal of work.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>roll.die_faces</t>
+          <t>roll.dice</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>faces</t>
+          <t>dice</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>How many faces each die has.</t>
+          <t>How many dice are thrown for an attempt. Two gives a bell: middling results are common, extremes are rare.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>light.ambient</t>
+          <t>roll.die_faces</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.14</v>
+        <v>6</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>faces</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>How much you can see where nothing is lighting the way. Very low: the labyrinth is dark, and light is something you carry into it.</t>
+          <t>How many faces each die has.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>light.warmth</t>
+          <t>light.ambient</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.45</v>
+        <v>0.14</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -10717,118 +10717,118 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>How much a lit thing goes orange rather than just brighter. 0 is cold light, 1 is firelight.</t>
+          <t>How much you can see where nothing is lighting the way. Very low: the labyrinth is dark, and light is something you carry into it.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>light.steps</t>
+          <t>light.warmth</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>0.45</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>steps</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>How many levels of brightness there are between dark and fully lit. Few levels look painted; many look smooth and cost more to draw.</t>
+          <t>How much a lit thing goes orange rather than just brighter. 0 is cold light, 1 is firelight.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>light.falloff</t>
+          <t>light.steps</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>steps</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>How sharply light dies with distance. Above 1 keeps the bright part close to the source.</t>
+          <t>How many levels of brightness there are between dark and fully lit. Few levels look painted; many look smooth and cost more to draw.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>anim.step_ticks</t>
+          <t>light.falloff</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22</v>
+        <v>1.35</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
+          <t>How sharply light dies with distance. Above 1 keeps the bright part close to the source.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>camera.follow</t>
+          <t>anim.step_ticks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0 or 1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
+          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>world.room_named_chance</t>
+          <t>camera.follow</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>0 or 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
+          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>world.room_condition_chance</t>
+          <t>world.room_named_chance</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10837,18 +10837,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
+          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>world.room_people_chance</t>
+          <t>world.room_condition_chance</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10857,78 +10857,78 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
+          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>world.room_shape_ramps</t>
+          <t>world.room_people_chance</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ways up</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
+          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>world.room_shape_min_side</t>
+          <t>world.room_shape_ramps</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>ways up</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
+          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>world.join_min</t>
+          <t>world.room_shape_min_side</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>doorways</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The fewest ways out of a piece into the piece next door. One is the smallest number that keeps the promise that you can always walk onward, so this dial must never be set below 1.</t>
+          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>world.join_max</t>
+          <t>world.join_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10937,14 +10937,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The most ways out of a piece into the piece next door. Every doorway is dug from the edge of the piece to one of its rooms, so more doorways means more corridors, more ways round, and fewer rooms left sealed off.</t>
+          <t>The fewest ways out of a piece into the piece next door. One is the smallest number that keeps the promise that you can always walk onward, so this dial must never be set below 1.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>world.join_margin</t>
+          <t>world.join_max</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -10952,83 +10952,83 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>tiles</t>
+          <t>doorways</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>How far a doorway keeps from the corner of a piece. Doorways from all four neighbouring pieces crowd into a corner, so this is what stops the four corners of the world meeting in one heap.</t>
+          <t>The most ways out of a piece into the piece next door. Every doorway is dug from the edge of the piece to one of its rooms, so more doorways means more corridors, more ways round, and fewer rooms left sealed off.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>room.study_difficulty</t>
+          <t>world.join_margin</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>tiles</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
+          <t>How far a doorway keeps from the corner of a piece. Doorways from all four neighbouring pieces crowd into a corner, so this is what stops the four corners of the world meeting in one heap.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>room.study_ticks</t>
+          <t>room.study_difficulty</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>How long a crawler spends looking at a room between attempts to read it.</t>
+          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>texture.masonry_mortar</t>
+          <t>room.study_ticks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.38</v>
+        <v>45</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
+          <t>How long a crawler spends looking at a room between attempts to read it.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>texture.masonry_variation</t>
+          <t>texture.masonry_mortar</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11037,38 +11037,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>texture.masonry_course_min</t>
+          <t>texture.masonry_variation</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The shortest a course of stones may be, about 9cm.</t>
+          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>texture.masonry_course_max</t>
+          <t>texture.masonry_course_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11077,18 +11077,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+          <t>The shortest a course of stones may be, about 9cm.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_min</t>
+          <t>texture.masonry_course_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11097,18 +11097,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>The narrowest a single stone may be.</t>
+          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_max</t>
+          <t>texture.masonry_stone_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11117,18 +11117,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
+          <t>The narrowest a single stone may be.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>texture.pattern_px</t>
+          <t>texture.masonry_stone_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11137,65 +11137,85 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
+          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>texture.hue_shift</t>
+          <t>texture.pattern_px</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.28</v>
+        <v>32</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>pixels</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
+          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>world.chunks_per_frame</t>
+          <t>texture.hue_shift</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>0.28</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>How many new pieces of labyrinth the game may cut in one frame of the picture (60 frames a second). A piece is real work to make, so they arrive a few at a time rather than all at once, and the picture stays smooth. Raise it to lay ground down faster; lower it if walking into new ground ever stutters.</t>
+          <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>world.chunks_per_frame</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>pieces</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>How many new pieces of labyrinth the game may cut in one frame of the picture (60 frames a second). A piece is real work to make, so they arrive a few at a time rather than all at once, and the picture stays smooth. Raise it to lay ground down faster; lower it if walking into new ground ever stutters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>world.live_ring</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B92" t="n">
         <v>1</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>pieces</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>How many pieces of ground are kept ready BEYOND what you can see, and beyond every crawler and every camp site. This ring is what stops a crawler reaching ground that has not been made yet. Every piece kept is a piece's worth of rooms held in memory and walked over by the picture, so a bigger ring is heavier: raise it only if new ground ever appears too late.</t>
         </is>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How solid the rock standing in front of a room stays. 0 means it is not painted at all and the room is seen straight through the gap; 1 means it is drawn like any other rock. Anything in between is the haze the game used to have.</t>
+          <t>How solid the rock standing in front of a room stays. 0 means it is not painted at all and the room is seen straight through the gap; 1 means it is drawn like any other rock. Anything in between is the haze the game used to have. Turned up to 1 in v0.44.0: the gap through the near rock was what left a black notch wherever two hidden blocks met, and the player asked to stop seeing through it. What it costs, measured at the camp over 4 seeds and 13,885 crawler pixels -- 2.9% of a crawler is hidden with the rock cut away and 18.7% with it solid, and 2 of the 4 seeds hide one crawler 86-96%. Below 1 turns the notch hunt back on.</t>
         </is>
       </c>
     </row>

--- a/docs/crawlers.xlsx
+++ b/docs/crawlers.xlsx
@@ -9375,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10784,91 +10784,91 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>anim.step_ticks</t>
+          <t>light.lamp_height</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22</v>
+        <v>0.9</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
+          <t>How high above the floor the light a crawler carries hangs -- about the height of a hand. It is why a wall is bright near the lamp and dimmer further up it.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>camera.follow</t>
+          <t>light.fire_height</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0 or 1</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
+          <t>How high above the ground the light of a burning structure sits -- knee height for a campfire. The floor round a fire is therefore brighter than a wall three metres up.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>world.room_named_chance</t>
+          <t>light.height_falloff</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
+          <t>How much height counts as distance for light. 0 lights every height the same, which is the flat look; 1 is true; raise it to exaggerate the darkening with height.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>world.room_condition_chance</t>
+          <t>light.smooth</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>0 or 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
+          <t>Whether brightness is painted as a smooth ramp (1) or in the few flat levels of light.steps (0). Smooth is the look; 0 is the cheaper fallback, and is what light.steps is for.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>world.room_people_chance</t>
+          <t>light.shade_strength</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10877,38 +10877,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
+          <t>How much of the light a cast shadow takes away. 0.5 halves it, which is what a fire behind a crawler looks like; 1 would leave a black hole where the shadow is.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>world.room_shape_ramps</t>
+          <t>light.shade_give</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ways up</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
+          <t>How far a shadow's edge takes to fade out. 0 is a hard stencil edge; 0.3 gives the edge about a third of a metre of give, which is the firm-but-not-cut-out look. Purely how it looks: light level and shadows never touch the simulation.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>world.room_shape_min_side</t>
+          <t>light.shade_reach</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10917,118 +10917,118 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
+          <t>How far from the thing casting it a shadow may stretch before it is cut off. A point light at knee height would throw a shadow as long as the thing is far from it, which smears across a room; this keeps them short.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>world.join_min</t>
+          <t>light.shade_girth</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>doorways</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The fewest ways out of a piece into the piece next door. One is the smallest number that keeps the promise that you can always walk onward, so this dial must never be set below 1.</t>
+          <t>How wide a thing has to be before it casts a shadow wider than a knife edge. About a hand. Small props and a crawler are roughly this thick, so their shadows have a body to them instead of being a line.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>world.join_max</t>
+          <t>anim.step_ticks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>doorways</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>The most ways out of a piece into the piece next door. Every doorway is dug from the edge of the piece to one of its rooms, so more doorways means more corridors, more ways round, and fewer rooms left sealed off.</t>
+          <t>How long a crawler takes to walk from one square to the next. Shorter than the pause between attempts, so they arrive and then think about the next step rather than gliding forever.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>world.join_margin</t>
+          <t>camera.follow</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>tiles</t>
+          <t>0 or 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>How far a doorway keeps from the corner of a piece. Doorways from all four neighbouring pieces crowd into a corner, so this is what stops the four corners of the world meeting in one heap.</t>
+          <t>Whether clicking a crawler locks the view onto them. 1 follows; 0 leaves the view where you put it. Panning by hand always lets go.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>room.study_difficulty</t>
+          <t>world.room_named_chance</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
+          <t>How many rooms are a PLACE -- a cistern, an arena -- rather than a plain hall. At 0.5 about half of them are something. The rest are bare rock, which is what makes the named ones land.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>room.study_ticks</t>
+          <t>world.room_condition_chance</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>45</v>
+        <v>0.55</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ticks</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>How long a crawler spends looking at a room between attempts to read it.</t>
+          <t>Chance a named room picks up a condition on top of what it was: flooded, burnt, haunted. Rolled twice, so two conditions can stack -- a haunted abandoned goblin slave market.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>texture.masonry_mortar</t>
+          <t>world.room_people_chance</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11037,34 +11037,34 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
+          <t>Chance a named room says whose it was. Goblin, dwarven, monks'.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>texture.masonry_variation</t>
+          <t>world.room_shape_ramps</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>ways up</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+          <t>How many ways there are up from one level of a room to the next. 1 makes a ledge you must walk round to climb; 4 makes it an open slope.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>texture.masonry_course_min</t>
+          <t>world.room_shape_min_side</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -11072,39 +11072,39 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The shortest a course of stones may be, about 9cm.</t>
+          <t>A room whose inside is narrower than this stays flat. There is no room to put a pit in a corridor.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>texture.masonry_course_max</t>
+          <t>world.join_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>doorways</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+          <t>The fewest ways out of a piece into the piece next door. One is the smallest number that keeps the promise that you can always walk onward, so this dial must never be set below 1.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_min</t>
+          <t>world.join_max</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -11112,112 +11112,312 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>doorways</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>The narrowest a single stone may be.</t>
+          <t>The most ways out of a piece into the piece next door. Every doorway is dug from the edge of the piece to one of its rooms, so more doorways means more corridors, more ways round, and fewer rooms left sealed off.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>texture.masonry_stone_max</t>
+          <t>world.join_margin</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>tiles</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
+          <t>How far a doorway keeps from the corner of a piece. Doorways from all four neighbouring pieces crowd into a corner, so this is what stops the four corners of the world meeting in one heap.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>texture.pattern_px</t>
+          <t>room.study_difficulty</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>pixels</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
+          <t>What a crawler must beat, Studying, to work out what a place was. They roll their Intellect and Willpower plus 2d6 against it.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>texture.hue_shift</t>
+          <t>room.study_ticks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.28</v>
+        <v>45</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>ticks</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
+          <t>How long a crawler spends looking at a room between attempts to read it.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>world.chunks_per_frame</t>
+          <t>texture.masonry_mortar</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>0.38</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>How many new pieces of labyrinth the game may cut in one frame of the picture (60 frames a second). A piece is real work to make, so they arrive a few at a time rather than all at once, and the picture stays smooth. Raise it to lay ground down faster; lower it if walking into new ground ever stutters.</t>
+          <t>How dark the joints between the stones are. 0 loses the joints and the wall goes smooth; 1 is a wall of black lines.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>texture.masonry_variation</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>How much one stone differs in shade from the next. 0 is a wall of identical blocks; high values look like patchwork.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>texture.masonry_course_min</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>The shortest a course of stones may be, about 9cm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>texture.masonry_course_max</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>7</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>The tallest a course of stones may be, about 22cm. Widen the gap between this and the minimum for rubble; narrow it for neat ashlar courses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>texture.masonry_stone_min</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>The narrowest a single stone may be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>texture.masonry_stone_max</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>11</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>The widest a single stone may be. Big blocks packed among small ones is what makes it read as hand-laid rather than as brick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>texture.pattern_px</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>32</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>pixels</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>The size of every repeating material tile. At 32 pixels to the metre, 32 means a material repeats once per square metre and lines up with the grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>texture.hue_shift</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>How far a shaded face shifts towards cold blue instead of just going darker. Hue-shifted shadows are what stop a dark picture reading as grey mud. 0 is a flat multiply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>world.chunks_per_frame</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>pieces</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>How many new pieces of labyrinth the game may cut in one frame of the picture (60 frames a second). A piece is real work to make, so they arrive a few at a time rather than all at once, and the picture stays smooth. Raise it to lay ground down faster; lower it if walking into new ground ever stutters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>world.live_ring</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B100" t="n">
         <v>1</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>pieces</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>How many pieces of ground are kept ready BEYOND what you can see, and beyond every crawler and every camp site. This ring is what stops a crawler reaching ground that has not been made yet. Every piece kept is a piece's worth of rooms held in memory and walked over by the picture, so a bigger ring is heavier: raise it only if new ground ever appears too late.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>light.across_min</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>The smallest unevenness of light along a wall worth painting a ramp across. ZERO: every difference, however small, because a wall's light is not supposed to be quantised at all and a bigger threshold loses seams it should keep. Raised, it spares a fill on faces whose ends agree closely with their own square.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>render.wrap_blend</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Parked at 0. A tiling surface should wrap and this one does not, so the repeat can be closed -- but it was built to fix the vertical join between two wall blocks and it does NOT: measured, closing every picture to 0.00 moved the join 15.6 -&gt; 15.3, i.e. nowhere. The join is the wall's own material map, not the tile. 0 is a plain copy, which leaves the picture identical to v0.51.0; the knob is kept because the defect is real and that job will want it.</t>
         </is>
       </c>
     </row>
@@ -11341,7 +11541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11897,6 +12097,18 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>nobody has read this place yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ui.label_light</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>light</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13829,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clambering</t>
+          <t>Focusing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13672,7 +13884,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wrangling</t>
+          <t>Grappling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13727,7 +13939,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Brawling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13752,7 +13964,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ranging</t>
+          <t>Maneuvering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13765,7 +13977,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Covering ground: travelling far, moving quietly, getting back again. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+          <t>Covering ground: travelling far, keeping pace, and getting back over rough going. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
       </c>
     </row>
@@ -13777,7 +13989,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Performing</t>
+          <t>Entertaining</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13802,7 +14014,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Sneaking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13810,17 +14022,12 @@
           <t>agility:1,intellect:1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
       <c r="E9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Making and mending: tools, clothes, meals, anything that takes hands and a recipe. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+          <t>Moving quietly, hiding, and going unseen in the dark. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
       </c>
     </row>
@@ -13850,7 +14057,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Locks, traps, and anything fiddly that punishes a shaking hand. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
+          <t>Making and mending: tools, clothes, meals, and anything else fiddly that punishes a shaking hand — locks, traps. (Every skill is one pair of the six attributes; all fifteen pairs exist.)</t>
         </is>
       </c>
     </row>
@@ -13912,7 +14119,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Enduring</t>
+          <t>Persisting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
